--- a/presentations/Analiz_NPA_FZ_426_dokumenty_SOUT.xlsx
+++ b/presentations/Analiz_NPA_FZ_426_dokumenty_SOUT.xlsx
@@ -2096,7 +2096,7 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>УКЭП</t>
+          <t>собственноручная или УКЭП</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">

--- a/presentations/Analiz_NPA_FZ_426_dokumenty_SOUT.xlsx
+++ b/presentations/Analiz_NPA_FZ_426_dokumenty_SOUT.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,6 +32,11 @@
     </font>
     <font>
       <name val="Times New Roman"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -76,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -89,6 +94,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -576,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="28" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" style="2" min="1" max="1"/>
@@ -590,7 +598,7 @@
     <col width="18" customWidth="1" style="2" min="9" max="15"/>
     <col width="24" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="28" customWidth="1" min="12" max="12"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
     <col width="28" customWidth="1" min="13" max="13"/>
     <col width="36" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
@@ -655,37 +663,42 @@
           <t>Передача в ГИС</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
+        <is>
+          <t>Что передается</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Название ГИС или реестра </t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Участник передачи документа СУОТ в ГИС (работник, работодатель, руководитель, специалист по ОТ, включая третьих лиц:  СФР, ГИТ, профсоюзы, аккредитованные организации и пр.)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Роль участника передачи документа СУОТ в ГИС (инициация, согласование, подписание, передача и т.д)</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>требования к хранению (да/нет)</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>место хранения</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>сроки  хранения</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>форма хранения</t>
         </is>
@@ -745,25 +758,30 @@
           <t>НЕТ</t>
         </is>
       </c>
-      <c r="L2" s="4" t="n"/>
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="M2" s="4" t="n"/>
       <c r="N2" s="4" t="n"/>
-      <c r="O2" s="4" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
+      <c r="O2" s="4" t="n"/>
       <c r="P2" s="4" t="inlineStr">
         <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="Q2" s="4" t="inlineStr">
+        <is>
           <t>У работодателя по месту проведения СОУТ</t>
         </is>
       </c>
-      <c r="Q2" s="4" t="inlineStr">
+      <c r="R2" s="4" t="inlineStr">
         <is>
           <t>45 лет (как документ к материалам СОУТ / решение по организации СОУТ; п. 407 Перечня Росархива № 236 — по аналогии с решениями к СОУТ)</t>
         </is>
       </c>
-      <c r="R2" s="4" t="inlineStr">
+      <c r="S2" s="4" t="inlineStr">
         <is>
           <t>Бумажная</t>
         </is>
@@ -823,25 +841,30 @@
           <t>НЕТ</t>
         </is>
       </c>
-      <c r="L3" s="4" t="n"/>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="M3" s="4" t="n"/>
       <c r="N3" s="4" t="n"/>
-      <c r="O3" s="4" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
+      <c r="O3" s="4" t="n"/>
       <c r="P3" s="4" t="inlineStr">
         <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
           <t>У работодателя по месту проведения СОУТ</t>
         </is>
       </c>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="R3" s="4" t="inlineStr">
         <is>
           <t>45 лет по месту проведения СОУТ; при вредных/опасных условиях труда — 50 лет (документы, законченные делопроизводством после 01.01.2003) / 75 лет (до 01.01.2003); в других организациях — 5 лет (п. 407 Перечня, утв. приказом Росархива от 20.12.2019 № 236)</t>
         </is>
       </c>
-      <c r="R3" s="4" t="inlineStr">
+      <c r="S3" s="4" t="inlineStr">
         <is>
           <t>Бумажная</t>
         </is>
@@ -903,35 +926,40 @@
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
+          <t>Сведения о рабочих местах (индивидуальный номер РМ, профессия/должность, численность работников, класс/подкласс условий труда и связанные показатели) в составе результатов СОУТ — ст. 18 ч. 2</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
           <t>Федеральная государственная информационная система учета результатов проведения специальной оценки условий труда (ФГИС учета результатов СОУТ)</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>Организация, проводящая СОУТ; Работодатель; Комиссия по СОУТ</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>Комиссия по СОУТ — утверждает перечень; Организация, проводящая СОУТ — передаёт сведения о рабочих местах в составе результатов СОУТ; Работодатель — обеспечивает проведение СОУТ</t>
         </is>
       </c>
-      <c r="O4" s="4" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
       <c r="P4" s="4" t="inlineStr">
         <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
           <t>У работодателя по месту проведения СОУТ</t>
         </is>
       </c>
-      <c r="Q4" s="4" t="inlineStr">
+      <c r="R4" s="4" t="inlineStr">
         <is>
           <t>45 лет по месту проведения СОУТ; при вредных/опасных условиях труда — 50 лет (документы, законченные делопроизводством после 01.01.2003) / 75 лет (до 01.01.2003); в других организациях — 5 лет (п. 407 Перечня, утв. приказом Росархива от 20.12.2019 № 236)</t>
         </is>
       </c>
-      <c r="R4" s="4" t="inlineStr">
+      <c r="S4" s="4" t="inlineStr">
         <is>
           <t>Бумажная и электронная</t>
         </is>
@@ -993,27 +1021,32 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
+          <t>Сведения о работодателе и об организации, проводящей СОУТ (для присвоения идентификационного номера предстоящей СОУТ) — ст. 8 ч. 6, ст. 18 (подп. «а», «в», «в.1» п. 1 ч. 2 и др.)</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
           <t>Федеральная государственная информационная система учета результатов проведения специальной оценки условий труда (ФГИС учета результатов СОУТ)</t>
         </is>
       </c>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>Организация, проводящая СОУТ; Работодатель</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
+      <c r="O5" s="4" t="inlineStr">
         <is>
           <t>Организация, проводящая СОУТ — передаёт в ФГИС сведения после заключения договора и получает идентификационный номер; Работодатель — заключает договор, получает идентификационный номер</t>
         </is>
       </c>
-      <c r="O5" s="4" t="inlineStr">
+      <c r="P5" s="4" t="inlineStr">
         <is>
           <t>НЕТ</t>
         </is>
       </c>
-      <c r="P5" s="4" t="n"/>
       <c r="Q5" s="4" t="n"/>
       <c r="R5" s="4" t="n"/>
+      <c r="S5" s="4" t="n"/>
     </row>
     <row r="6" ht="75" customHeight="1">
       <c r="A6" s="4" t="n">
@@ -1071,35 +1104,40 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
+          <t>Полностью документ</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
           <t>Федеральная государственная информационная система учета результатов проведения специальной оценки условий труда (ФГИС учета результатов СОУТ)</t>
         </is>
       </c>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="N6" s="4" t="inlineStr">
         <is>
           <t>Организация, проводящая СОУТ; Работодатель; Комиссия по СОУТ; Председатель комиссии по СОУТ</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <t>Члены комиссии — подписывают отчет; Председатель комиссии — утверждает отчет; Работодатель — уведомляет организацию СОУТ и направляет копию утвержденного отчета; Организация, проводящая СОУТ — передаёт сведения о результатах в ФГИС</t>
         </is>
       </c>
-      <c r="O6" s="4" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
       <c r="P6" s="4" t="inlineStr">
         <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="Q6" s="4" t="inlineStr">
+        <is>
           <t>У работодателя по месту проведения СОУТ; экземпляр/сведения также у организации, проводившей СОУТ</t>
         </is>
       </c>
-      <c r="Q6" s="4" t="inlineStr">
+      <c r="R6" s="4" t="inlineStr">
         <is>
           <t>45 лет по месту проведения СОУТ; при вредных/опасных условиях труда — 50 лет (документы, законченные делопроизводством после 01.01.2003) / 75 лет (до 01.01.2003); в других организациях — 5 лет (п. 407 Перечня, утв. приказом Росархива от 20.12.2019 № 236)</t>
         </is>
       </c>
-      <c r="R6" s="4" t="inlineStr">
+      <c r="S6" s="4" t="inlineStr">
         <is>
           <t>Бумажная и электронная</t>
         </is>
@@ -1161,35 +1199,40 @@
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
+          <t>Сведения по рабочему месту: класс (подкласс) условий труда, вредные/опасные факторы, измеренные значения, продолжительность воздействия, сведения о снижении класса на основании оценки эффективности СИЗ — ст. 18 ч. 2</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
           <t>Федеральная государственная информационная система учета результатов проведения специальной оценки условий труда (ФГИС учета результатов СОУТ)</t>
         </is>
       </c>
-      <c r="M7" s="4" t="inlineStr">
+      <c r="N7" s="4" t="inlineStr">
         <is>
           <t>Организация, проводящая СОУТ; Комиссия по СОУТ; Работник</t>
         </is>
       </c>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="O7" s="4" t="inlineStr">
         <is>
           <t>Организация, проводящая СОУТ — формирует карты и передаёт сведения в ФГИС; Комиссия по СОУТ — утверждает в составе отчета; Работник — ознакамливается с результатами</t>
         </is>
       </c>
-      <c r="O7" s="4" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="Q7" s="4" t="inlineStr">
+        <is>
           <t>У работодателя по месту проведения СОУТ</t>
         </is>
       </c>
-      <c r="Q7" s="4" t="inlineStr">
+      <c r="R7" s="4" t="inlineStr">
         <is>
           <t>45 лет по месту проведения СОУТ; при вредных/опасных условиях труда — 50 лет (документы, законченные делопроизводством после 01.01.2003) / 75 лет (до 01.01.2003); в других организациях — 5 лет (п. 407 Перечня, утв. приказом Росархива от 20.12.2019 № 236)</t>
         </is>
       </c>
-      <c r="R7" s="4" t="inlineStr">
+      <c r="S7" s="4" t="inlineStr">
         <is>
           <t>Бумажная и электронная</t>
         </is>
@@ -1251,35 +1294,40 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
+          <t>Сведения о рабочих местах, на которых проведена СОУТ, и распределение по классам (подклассам) условий труда — ст. 18</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
           <t>Федеральная государственная информационная система учета результатов проведения специальной оценки условий труда (ФГИС учета результатов СОУТ)</t>
         </is>
       </c>
-      <c r="M8" s="4" t="inlineStr">
+      <c r="N8" s="4" t="inlineStr">
         <is>
           <t>Организация, проводящая СОУТ; Комиссия по СОУТ</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="O8" s="4" t="inlineStr">
         <is>
           <t>Организация, проводящая СОУТ — формирует и передаёт сведения в ФГИС; Комиссия по СОУТ — утверждает в составе отчета</t>
         </is>
       </c>
-      <c r="O8" s="4" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="Q8" s="4" t="inlineStr">
+        <is>
           <t>У работодателя по месту проведения СОУТ</t>
         </is>
       </c>
-      <c r="Q8" s="4" t="inlineStr">
+      <c r="R8" s="4" t="inlineStr">
         <is>
           <t>45 лет по месту проведения СОУТ; при вредных/опасных условиях труда — 50 лет (документы, законченные делопроизводством после 01.01.2003) / 75 лет (до 01.01.2003); в других организациях — 5 лет (п. 407 Перечня, утв. приказом Росархива от 20.12.2019 № 236)</t>
         </is>
       </c>
-      <c r="R8" s="4" t="inlineStr">
+      <c r="S8" s="4" t="inlineStr">
         <is>
           <t>Бумажная и электронная</t>
         </is>
@@ -1341,35 +1389,40 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
+          <t>Измеренные значения вредных и (или) опасных производственных факторов, единицы измерения, нормативы, продолжительность воздействия — ст. 18 ч. 2</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
           <t>Федеральная государственная информационная система учета результатов проведения специальной оценки условий труда (ФГИС учета результатов СОУТ)</t>
         </is>
       </c>
-      <c r="M9" s="4" t="inlineStr">
+      <c r="N9" s="4" t="inlineStr">
         <is>
           <t>Организация, проводящая СОУТ; Комиссия по СОУТ</t>
         </is>
       </c>
-      <c r="N9" s="4" t="inlineStr">
+      <c r="O9" s="4" t="inlineStr">
         <is>
           <t>Организация, проводящая СОУТ — оформляет протоколы и передаёт сведения измерений в ФГИС; Комиссия по СОУТ — принимает результаты в рамках отчета</t>
         </is>
       </c>
-      <c r="O9" s="4" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="Q9" s="4" t="inlineStr">
+        <is>
           <t>У работодателя по месту проведения СОУТ</t>
         </is>
       </c>
-      <c r="Q9" s="4" t="inlineStr">
+      <c r="R9" s="4" t="inlineStr">
         <is>
           <t>45 лет по месту проведения СОУТ; при вредных/опасных условиях труда — 50 лет (документы, законченные делопроизводством после 01.01.2003) / 75 лет (до 01.01.2003); в других организациях — 5 лет (п. 407 Перечня, утв. приказом Росархива от 20.12.2019 № 236)</t>
         </is>
       </c>
-      <c r="R9" s="4" t="inlineStr">
+      <c r="S9" s="4" t="inlineStr">
         <is>
           <t>Бумажная и электронная</t>
         </is>
@@ -1431,35 +1484,40 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
+          <t>Сведения о снижении класса (подкласса) условий труда на основании оценки эффективности СИЗ, включая реквизиты протокола — ст. 18 ч. 2</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
           <t>Федеральная государственная информационная система учета результатов проведения специальной оценки условий труда (ФГИС учета результатов СОУТ)</t>
         </is>
       </c>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="N10" s="4" t="inlineStr">
         <is>
           <t>Организация, проводящая СОУТ; Комиссия по СОУТ</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="O10" s="4" t="inlineStr">
         <is>
           <t>Организация, проводящая СОУТ — оформляет протокол и передаёт сведения в ФГИС; Комиссия по СОУТ — утверждает в составе отчета</t>
         </is>
       </c>
-      <c r="O10" s="4" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="Q10" s="4" t="inlineStr">
+        <is>
           <t>У работодателя по месту проведения СОУТ</t>
         </is>
       </c>
-      <c r="Q10" s="4" t="inlineStr">
+      <c r="R10" s="4" t="inlineStr">
         <is>
           <t>45 лет по месту проведения СОУТ; при вредных/опасных условиях труда — 50 лет (документы, законченные делопроизводством после 01.01.2003) / 75 лет (до 01.01.2003); в других организациях — 5 лет (п. 407 Перечня, утв. приказом Росархива от 20.12.2019 № 236)</t>
         </is>
       </c>
-      <c r="R10" s="4" t="inlineStr">
+      <c r="S10" s="4" t="inlineStr">
         <is>
           <t>Бумажная и электронная</t>
         </is>
@@ -1519,33 +1577,38 @@
           <t>НЕТ</t>
         </is>
       </c>
-      <c r="L11" s="4" t="n"/>
-      <c r="M11" s="4" t="inlineStr">
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="n"/>
+      <c r="N11" s="4" t="inlineStr">
         <is>
           <t>Работодатель; Территориальный орган ГИТ</t>
         </is>
       </c>
-      <c r="N11" s="4" t="inlineStr">
+      <c r="O11" s="4" t="inlineStr">
         <is>
           <t>Работодатель — направляет копию протокола в территориальный орган ГИТ; ГИТ — получает копию</t>
         </is>
       </c>
-      <c r="O11" s="4" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="Q11" s="4" t="inlineStr">
+        <is>
           <t>У работодателя по месту проведения СОУТ</t>
         </is>
       </c>
-      <c r="Q11" s="4" t="inlineStr">
+      <c r="R11" s="4" t="inlineStr">
         <is>
           <t>45 лет по месту проведения СОУТ; при вредных/опасных условиях труда — 50 лет (документы, законченные делопроизводством после 01.01.2003) / 75 лет (до 01.01.2003); в других организациях — 5 лет (п. 407 Перечня, утв. приказом Росархива от 20.12.2019 № 236)</t>
         </is>
       </c>
-      <c r="R11" s="4" t="inlineStr">
+      <c r="S11" s="4" t="inlineStr">
         <is>
           <t>Бумажная и электронная</t>
         </is>
@@ -1607,35 +1670,40 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
+          <t>Сводные сведения о количестве рабочих мест и распределении рабочих мест по классам (подклассам) условий труда — ст. 18 ч. 2</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
           <t>Федеральная государственная информационная система учета результатов проведения специальной оценки условий труда (ФГИС учета результатов СОУТ)</t>
         </is>
       </c>
-      <c r="M12" s="4" t="inlineStr">
+      <c r="N12" s="4" t="inlineStr">
         <is>
           <t>Организация, проводящая СОУТ; Работодатель; Комиссия по СОУТ</t>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="O12" s="4" t="inlineStr">
         <is>
           <t>Организация, проводящая СОУТ — формирует и передаёт сведения в ФГИС; Комиссия по СОУТ — утверждает в составе отчета; Работодатель — размещает сводные данные на сайте (при наличии)</t>
         </is>
       </c>
-      <c r="O12" s="4" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="Q12" s="4" t="inlineStr">
+        <is>
           <t>У работодателя по месту проведения СОУТ</t>
         </is>
       </c>
-      <c r="Q12" s="4" t="inlineStr">
+      <c r="R12" s="4" t="inlineStr">
         <is>
           <t>45 лет по месту проведения СОУТ; при вредных/опасных условиях труда — 50 лет (документы, законченные делопроизводством после 01.01.2003) / 75 лет (до 01.01.2003); в других организациях — 5 лет (п. 407 Перечня, утв. приказом Росархива от 20.12.2019 № 236)</t>
         </is>
       </c>
-      <c r="R12" s="4" t="inlineStr">
+      <c r="S12" s="4" t="inlineStr">
         <is>
           <t>Бумажная и электронная</t>
         </is>
@@ -1695,25 +1763,30 @@
           <t>НЕТ</t>
         </is>
       </c>
-      <c r="L13" s="4" t="n"/>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="M13" s="4" t="n"/>
       <c r="N13" s="4" t="n"/>
-      <c r="O13" s="4" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
+      <c r="O13" s="4" t="n"/>
       <c r="P13" s="4" t="inlineStr">
         <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="Q13" s="4" t="inlineStr">
+        <is>
           <t>У работодателя по месту проведения СОУТ</t>
         </is>
       </c>
-      <c r="Q13" s="4" t="inlineStr">
+      <c r="R13" s="4" t="inlineStr">
         <is>
           <t>45 лет по месту проведения СОУТ; при вредных/опасных условиях труда — 50 лет (документы, законченные делопроизводством после 01.01.2003) / 75 лет (до 01.01.2003); в других организациях — 5 лет (п. 407 Перечня, утв. приказом Росархива от 20.12.2019 № 236)</t>
         </is>
       </c>
-      <c r="R13" s="4" t="inlineStr">
+      <c r="S13" s="4" t="inlineStr">
         <is>
           <t>Бумажная и электронная</t>
         </is>
@@ -1775,35 +1848,40 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
+          <t>Сведения о результатах проведения СОУТ (классы/подклассы, факторы и связанные данные учета) — ст. 18</t>
+        </is>
+      </c>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
           <t>Федеральная государственная информационная система учета результатов проведения специальной оценки условий труда (ФГИС учета результатов СОУТ)</t>
         </is>
       </c>
-      <c r="M14" s="4" t="inlineStr">
+      <c r="N14" s="4" t="inlineStr">
         <is>
           <t>Эксперт организации, проводящей СОУТ; Организация, проводящая СОУТ; Комиссия по СОУТ</t>
         </is>
       </c>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="O14" s="4" t="inlineStr">
         <is>
           <t>Эксперт — готовит заключение; Организация, проводящая СОУТ — передаёт результаты в ФГИС; Комиссия по СОУТ — утверждает отчет</t>
         </is>
       </c>
-      <c r="O14" s="4" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="Q14" s="4" t="inlineStr">
+        <is>
           <t>У работодателя по месту проведения СОУТ</t>
         </is>
       </c>
-      <c r="Q14" s="4" t="inlineStr">
+      <c r="R14" s="4" t="inlineStr">
         <is>
           <t>45 лет по месту проведения СОУТ; при вредных/опасных условиях труда — 50 лет (документы, законченные делопроизводством после 01.01.2003) / 75 лет (до 01.01.2003); в других организациях — 5 лет (п. 407 Перечня, утв. приказом Росархива от 20.12.2019 № 236)</t>
         </is>
       </c>
-      <c r="R14" s="4" t="inlineStr">
+      <c r="S14" s="4" t="inlineStr">
         <is>
           <t>Бумажная и электронная</t>
         </is>
@@ -1863,25 +1941,30 @@
           <t>НЕТ</t>
         </is>
       </c>
-      <c r="L15" s="4" t="n"/>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="M15" s="4" t="n"/>
       <c r="N15" s="4" t="n"/>
-      <c r="O15" s="4" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
+      <c r="O15" s="4" t="n"/>
       <c r="P15" s="4" t="inlineStr">
         <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="Q15" s="4" t="inlineStr">
+        <is>
           <t>У работодателя по месту проведения СОУТ</t>
         </is>
       </c>
-      <c r="Q15" s="4" t="inlineStr">
+      <c r="R15" s="4" t="inlineStr">
         <is>
           <t>45 лет по месту проведения СОУТ; при вредных/опасных условиях труда — 50 лет (документы, законченные делопроизводством после 01.01.2003) / 75 лет (до 01.01.2003); в других организациях — 5 лет (п. 407 Перечня, утв. приказом Росархива от 20.12.2019 № 236)</t>
         </is>
       </c>
-      <c r="R15" s="4" t="inlineStr">
+      <c r="S15" s="4" t="inlineStr">
         <is>
           <t>Бумажная</t>
         </is>
@@ -1941,25 +2024,30 @@
           <t>НЕТ</t>
         </is>
       </c>
-      <c r="L16" s="4" t="n"/>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="M16" s="4" t="n"/>
       <c r="N16" s="4" t="n"/>
-      <c r="O16" s="4" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
+      <c r="O16" s="4" t="n"/>
       <c r="P16" s="4" t="inlineStr">
         <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="Q16" s="4" t="inlineStr">
+        <is>
           <t>У работодателя по месту проведения СОУТ</t>
         </is>
       </c>
-      <c r="Q16" s="4" t="inlineStr">
+      <c r="R16" s="4" t="inlineStr">
         <is>
           <t>45 лет по месту проведения СОУТ; при вредных/опасных условиях труда — 50 лет (документы, законченные делопроизводством после 01.01.2003) / 75 лет (до 01.01.2003); в других организациях — 5 лет (п. 407 Перечня, утв. приказом Росархива от 20.12.2019 № 236)</t>
         </is>
       </c>
-      <c r="R16" s="4" t="inlineStr">
+      <c r="S16" s="4" t="inlineStr">
         <is>
           <t>Бумажная</t>
         </is>
@@ -2021,35 +2109,40 @@
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
+          <t>Полностью документ</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
           <t>Реестр деклараций соответствия условий труда государственным нормативным требованиям охраны труда; сведения о результатах СОУТ также учитываются в: Федеральная государственная информационная система учета результатов проведения специальной оценки условий труда (ФГИС учета результатов СОУТ)</t>
         </is>
       </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="N17" s="4" t="inlineStr">
         <is>
           <t>Работодатель; Территориальный орган ГИТ (уполномоченный орган); Организация, проводящая СОУТ</t>
         </is>
       </c>
-      <c r="N17" s="4" t="inlineStr">
+      <c r="O17" s="4" t="inlineStr">
         <is>
           <t>Работодатель — подаёт декларацию; Уполномоченный орган / ГИТ — формирует и ведёт реестр деклараций; Организация, проводящая СОУТ — передаёт связанные результаты СОУТ в ФГИС</t>
         </is>
       </c>
-      <c r="O17" s="4" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="Q17" s="4" t="inlineStr">
+        <is>
           <t>У работодателя по месту проведения СОУТ; реестр ведётся уполномоченным органом</t>
         </is>
       </c>
-      <c r="Q17" s="4" t="inlineStr">
+      <c r="R17" s="4" t="inlineStr">
         <is>
           <t>45 лет по месту проведения СОУТ; при вредных/опасных условиях труда — 50 лет (документы, законченные делопроизводством после 01.01.2003) / 75 лет (до 01.01.2003); в других организациях — 5 лет (п. 407 Перечня, утв. приказом Росархива от 20.12.2019 № 236); декларация бессрочна при сохранении условий труда (ст. 11 ч. 4)</t>
         </is>
       </c>
-      <c r="R17" s="4" t="inlineStr">
+      <c r="S17" s="4" t="inlineStr">
         <is>
           <t>Бумажная и электронная</t>
         </is>
@@ -2109,25 +2202,30 @@
           <t>НЕТ</t>
         </is>
       </c>
-      <c r="L18" s="4" t="n"/>
-      <c r="M18" s="4" t="inlineStr">
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M18" s="4" t="n"/>
+      <c r="N18" s="4" t="inlineStr">
         <is>
           <t>Работодатель; Организация, проводившая СОУТ</t>
         </is>
       </c>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="O18" s="4" t="inlineStr">
         <is>
           <t>Работодатель — уведомляет и направляет копию; Организация, проводившая СОУТ — получает копию и далее передаёт сведения в ФГИС</t>
         </is>
       </c>
-      <c r="O18" s="4" t="inlineStr">
+      <c r="P18" s="4" t="inlineStr">
         <is>
           <t>НЕТ</t>
         </is>
       </c>
-      <c r="P18" s="4" t="n"/>
       <c r="Q18" s="4" t="n"/>
       <c r="R18" s="4" t="n"/>
+      <c r="S18" s="4" t="n"/>
     </row>
     <row r="19" ht="75" customHeight="1">
       <c r="A19" s="4" t="n">
@@ -2183,25 +2281,30 @@
           <t>НЕТ</t>
         </is>
       </c>
-      <c r="L19" s="4" t="n"/>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="M19" s="4" t="n"/>
       <c r="N19" s="4" t="n"/>
-      <c r="O19" s="4" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
+      <c r="O19" s="4" t="n"/>
       <c r="P19" s="4" t="inlineStr">
         <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="Q19" s="4" t="inlineStr">
+        <is>
           <t>У работодателя по месту проведения СОУТ</t>
         </is>
       </c>
-      <c r="Q19" s="4" t="inlineStr">
+      <c r="R19" s="4" t="inlineStr">
         <is>
           <t>45 лет по месту проведения СОУТ; при вредных/опасных условиях труда — 50 лет (документы, законченные делопроизводством после 01.01.2003) / 75 лет (до 01.01.2003); в других организациях — 5 лет (п. 407 Перечня, утв. приказом Росархива от 20.12.2019 № 236)</t>
         </is>
       </c>
-      <c r="R19" s="4" t="inlineStr">
+      <c r="S19" s="4" t="inlineStr">
         <is>
           <t>Бумажная</t>
         </is>
@@ -2261,17 +2364,22 @@
           <t>НЕТ</t>
         </is>
       </c>
-      <c r="L20" s="4" t="n"/>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="M20" s="4" t="n"/>
       <c r="N20" s="4" t="n"/>
-      <c r="O20" s="4" t="inlineStr">
+      <c r="O20" s="4" t="n"/>
+      <c r="P20" s="4" t="inlineStr">
         <is>
           <t>НЕТ</t>
         </is>
       </c>
-      <c r="P20" s="4" t="n"/>
       <c r="Q20" s="4" t="n"/>
       <c r="R20" s="4" t="n"/>
+      <c r="S20" s="4" t="n"/>
     </row>
     <row r="21" ht="75" customHeight="1">
       <c r="A21" s="4" t="n">
@@ -2327,25 +2435,30 @@
           <t>НЕТ</t>
         </is>
       </c>
-      <c r="L21" s="4" t="n"/>
-      <c r="M21" s="4" t="inlineStr">
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="n"/>
+      <c r="N21" s="4" t="inlineStr">
         <is>
           <t>Работодатель; Территориальный орган ГИТ</t>
         </is>
       </c>
-      <c r="N21" s="4" t="inlineStr">
+      <c r="O21" s="4" t="inlineStr">
         <is>
           <t>Работодатель — направляет копию; ГИТ — получает</t>
         </is>
       </c>
-      <c r="O21" s="4" t="inlineStr">
+      <c r="P21" s="4" t="inlineStr">
         <is>
           <t>НЕТ</t>
         </is>
       </c>
-      <c r="P21" s="4" t="n"/>
       <c r="Q21" s="4" t="n"/>
       <c r="R21" s="4" t="n"/>
+      <c r="S21" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/presentations/Analiz_NPA_FZ_426_dokumenty_SOUT.xlsx
+++ b/presentations/Analiz_NPA_FZ_426_dokumenty_SOUT.xlsx
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S21"/>
+  <dimension ref="A1:U21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="28" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" style="2" min="1" max="1"/>
@@ -595,9 +595,9 @@
     <col width="10" customWidth="1" style="2" min="6" max="8"/>
     <col width="36" customWidth="1" min="7" max="7"/>
     <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" style="2" min="9" max="15"/>
+    <col width="22" customWidth="1" style="2" min="9" max="15"/>
     <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
     <col width="40" customWidth="1" min="12" max="12"/>
     <col width="28" customWidth="1" min="13" max="13"/>
     <col width="36" customWidth="1" min="14" max="14"/>
@@ -648,57 +648,67 @@
           <t xml:space="preserve">Кто подписывает </t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>Возможность формирования электронного документа</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Вид подписи (собственноручная, ПЭП, НЭП, УКЭП)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>Наличие требований к ведению документа</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Требования к ведению документооборота (печать, нумерация, прошивка и т.п)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Передача в ГИС</t>
         </is>
       </c>
-      <c r="L1" s="5" t="inlineStr">
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>Что передается</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Название ГИС или реестра </t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Участник передачи документа СУОТ в ГИС (работник, работодатель, руководитель, специалист по ОТ, включая третьих лиц:  СФР, ГИТ, профсоюзы, аккредитованные организации и пр.)</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Роль участника передачи документа СУОТ в ГИС (инициация, согласование, подписание, передача и т.д)</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>требования к хранению (да/нет)</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>место хранения</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>сроки  хранения</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>форма хранения</t>
         </is>
@@ -745,43 +755,53 @@
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
           <t>собственноручная</t>
         </is>
       </c>
-      <c r="J2" s="4" t="inlineStr">
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="inlineStr">
         <is>
           <t>не предусмотрено</t>
         </is>
       </c>
-      <c r="K2" s="4" t="inlineStr">
+      <c r="M2" s="4" t="inlineStr">
         <is>
           <t>НЕТ</t>
         </is>
       </c>
-      <c r="L2" s="4" t="inlineStr">
+      <c r="N2" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M2" s="4" t="n"/>
-      <c r="N2" s="4" t="n"/>
       <c r="O2" s="4" t="n"/>
-      <c r="P2" s="4" t="inlineStr">
+      <c r="P2" s="4" t="n"/>
+      <c r="Q2" s="4" t="n"/>
+      <c r="R2" s="4" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="Q2" s="4" t="inlineStr">
+      <c r="S2" s="4" t="inlineStr">
         <is>
           <t>У работодателя по месту проведения СОУТ</t>
         </is>
       </c>
-      <c r="R2" s="4" t="inlineStr">
+      <c r="T2" s="4" t="inlineStr">
         <is>
           <t>45 лет (как документ к материалам СОУТ / решение по организации СОУТ; п. 407 Перечня Росархива № 236 — по аналогии с решениями к СОУТ)</t>
         </is>
       </c>
-      <c r="S2" s="4" t="inlineStr">
+      <c r="U2" s="4" t="inlineStr">
         <is>
           <t>Бумажная</t>
         </is>
@@ -828,43 +848,53 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
           <t>собственноручная</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>не предусмотрено</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>НЕТ</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M3" s="4" t="n"/>
-      <c r="N3" s="4" t="n"/>
       <c r="O3" s="4" t="n"/>
-      <c r="P3" s="4" t="inlineStr">
+      <c r="P3" s="4" t="n"/>
+      <c r="Q3" s="4" t="n"/>
+      <c r="R3" s="4" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="S3" s="4" t="inlineStr">
         <is>
           <t>У работодателя по месту проведения СОУТ</t>
         </is>
       </c>
-      <c r="R3" s="4" t="inlineStr">
+      <c r="T3" s="4" t="inlineStr">
         <is>
           <t>45 лет по месту проведения СОУТ; при вредных/опасных условиях труда — 50 лет (документы, законченные делопроизводством после 01.01.2003) / 75 лет (до 01.01.2003); в других организациях — 5 лет (п. 407 Перечня, утв. приказом Росархива от 20.12.2019 № 236)</t>
         </is>
       </c>
-      <c r="S3" s="4" t="inlineStr">
+      <c r="U3" s="4" t="inlineStr">
         <is>
           <t>Бумажная</t>
         </is>
@@ -911,55 +941,65 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
           <t>собственноручная</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>не предусмотрено</t>
-        </is>
-      </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>утверждение комиссией до начала работ по СОУТ; указание аналогичных рабочих мест</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
           <t>ЧАСТИЧНО</t>
         </is>
       </c>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>Сведения о рабочих местах (индивидуальный номер РМ, профессия/должность, численность работников, класс/подкласс условий труда и связанные показатели) в составе результатов СОУТ — ст. 18 ч. 2</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>Федеральная государственная информационная система учета результатов проведения специальной оценки условий труда (ФГИС учета результатов СОУТ)</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="P4" s="4" t="inlineStr">
         <is>
           <t>Организация, проводящая СОУТ; Работодатель; Комиссия по СОУТ</t>
         </is>
       </c>
-      <c r="O4" s="4" t="inlineStr">
+      <c r="Q4" s="4" t="inlineStr">
         <is>
           <t>Комиссия по СОУТ — утверждает перечень; Организация, проводящая СОУТ — передаёт сведения о рабочих местах в составе результатов СОУТ; Работодатель — обеспечивает проведение СОУТ</t>
         </is>
       </c>
-      <c r="P4" s="4" t="inlineStr">
+      <c r="R4" s="4" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="Q4" s="4" t="inlineStr">
+      <c r="S4" s="4" t="inlineStr">
         <is>
           <t>У работодателя по месту проведения СОУТ</t>
         </is>
       </c>
-      <c r="R4" s="4" t="inlineStr">
+      <c r="T4" s="4" t="inlineStr">
         <is>
           <t>45 лет по месту проведения СОУТ; при вредных/опасных условиях труда — 50 лет (документы, законченные делопроизводством после 01.01.2003) / 75 лет (до 01.01.2003); в других организациях — 5 лет (п. 407 Перечня, утв. приказом Росархива от 20.12.2019 № 236)</t>
         </is>
       </c>
-      <c r="S4" s="4" t="inlineStr">
+      <c r="U4" s="4" t="inlineStr">
         <is>
           <t>Бумажная и электронная</t>
         </is>
@@ -1006,47 +1046,57 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
           <t>собственноручная или УКЭП</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>не предусмотрено</t>
-        </is>
-      </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>заключение до начала работ; организация СОУТ не позднее 5 рабочих дней со дня заключения договора передаёт сведения в ФГИС и сообщает работодателю идентификационный номер</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
           <t>ЧАСТИЧНО</t>
         </is>
       </c>
-      <c r="L5" s="4" t="inlineStr">
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>Сведения о работодателе и об организации, проводящей СОУТ (для присвоения идентификационного номера предстоящей СОУТ) — ст. 8 ч. 6, ст. 18 (подп. «а», «в», «в.1» п. 1 ч. 2 и др.)</t>
         </is>
       </c>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="O5" s="4" t="inlineStr">
         <is>
           <t>Федеральная государственная информационная система учета результатов проведения специальной оценки условий труда (ФГИС учета результатов СОУТ)</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
+      <c r="P5" s="4" t="inlineStr">
         <is>
           <t>Организация, проводящая СОУТ; Работодатель</t>
         </is>
       </c>
-      <c r="O5" s="4" t="inlineStr">
+      <c r="Q5" s="4" t="inlineStr">
         <is>
           <t>Организация, проводящая СОУТ — передаёт в ФГИС сведения после заключения договора и получает идентификационный номер; Работодатель — заключает договор, получает идентификационный номер</t>
         </is>
       </c>
-      <c r="P5" s="4" t="inlineStr">
+      <c r="R5" s="4" t="inlineStr">
         <is>
           <t>НЕТ</t>
         </is>
       </c>
-      <c r="Q5" s="4" t="n"/>
-      <c r="R5" s="4" t="n"/>
       <c r="S5" s="4" t="n"/>
+      <c r="T5" s="4" t="n"/>
+      <c r="U5" s="4" t="n"/>
     </row>
     <row r="6" ht="75" customHeight="1">
       <c r="A6" s="4" t="n">
@@ -1089,55 +1139,65 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
           <t>собственноручная или НЭП или УКЭП</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>допускается бумажный носитель или электронный документ; утверждение не позднее 30 календарных дней со дня направления работодателю</t>
-        </is>
-      </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>бумажный носитель или электронный документ; подписание всеми членами комиссии; утверждение председателем комиссии не позднее 30 календарных дней со дня направления работодателю; наличие идентификационного номера; особое мнение члена комиссии прилагается письменно (при наличии)</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="L6" s="4" t="inlineStr">
+      <c r="N6" s="4" t="inlineStr">
         <is>
           <t>Полностью документ</t>
         </is>
       </c>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <t>Федеральная государственная информационная система учета результатов проведения специальной оценки условий труда (ФГИС учета результатов СОУТ)</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="P6" s="4" t="inlineStr">
         <is>
           <t>Организация, проводящая СОУТ; Работодатель; Комиссия по СОУТ; Председатель комиссии по СОУТ</t>
         </is>
       </c>
-      <c r="O6" s="4" t="inlineStr">
+      <c r="Q6" s="4" t="inlineStr">
         <is>
           <t>Члены комиссии — подписывают отчет; Председатель комиссии — утверждает отчет; Работодатель — уведомляет организацию СОУТ и направляет копию утвержденного отчета; Организация, проводящая СОУТ — передаёт сведения о результатах в ФГИС</t>
         </is>
       </c>
-      <c r="P6" s="4" t="inlineStr">
+      <c r="R6" s="4" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="Q6" s="4" t="inlineStr">
+      <c r="S6" s="4" t="inlineStr">
         <is>
           <t>У работодателя по месту проведения СОУТ; экземпляр/сведения также у организации, проводившей СОУТ</t>
         </is>
       </c>
-      <c r="R6" s="4" t="inlineStr">
+      <c r="T6" s="4" t="inlineStr">
         <is>
           <t>45 лет по месту проведения СОУТ; при вредных/опасных условиях труда — 50 лет (документы, законченные делопроизводством после 01.01.2003) / 75 лет (до 01.01.2003); в других организациях — 5 лет (п. 407 Перечня, утв. приказом Росархива от 20.12.2019 № 236)</t>
         </is>
       </c>
-      <c r="S6" s="4" t="inlineStr">
+      <c r="U6" s="4" t="inlineStr">
         <is>
           <t>Бумажная и электронная</t>
         </is>
@@ -1184,55 +1244,65 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
           <t>собственноручная или НЭП или УКЭП</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>на аналогичные рабочие места заполняется одна карта</t>
-        </is>
-      </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>оформляется в составе отчета; на аналогичные рабочие места заполняется одна карта</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
           <t>ЧАСТИЧНО</t>
         </is>
       </c>
-      <c r="L7" s="4" t="inlineStr">
+      <c r="N7" s="4" t="inlineStr">
         <is>
           <t>Сведения по рабочему месту: класс (подкласс) условий труда, вредные/опасные факторы, измеренные значения, продолжительность воздействия, сведения о снижении класса на основании оценки эффективности СИЗ — ст. 18 ч. 2</t>
         </is>
       </c>
-      <c r="M7" s="4" t="inlineStr">
+      <c r="O7" s="4" t="inlineStr">
         <is>
           <t>Федеральная государственная информационная система учета результатов проведения специальной оценки условий труда (ФГИС учета результатов СОУТ)</t>
         </is>
       </c>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="P7" s="4" t="inlineStr">
         <is>
           <t>Организация, проводящая СОУТ; Комиссия по СОУТ; Работник</t>
         </is>
       </c>
-      <c r="O7" s="4" t="inlineStr">
+      <c r="Q7" s="4" t="inlineStr">
         <is>
           <t>Организация, проводящая СОУТ — формирует карты и передаёт сведения в ФГИС; Комиссия по СОУТ — утверждает в составе отчета; Работник — ознакамливается с результатами</t>
         </is>
       </c>
-      <c r="P7" s="4" t="inlineStr">
+      <c r="R7" s="4" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="Q7" s="4" t="inlineStr">
+      <c r="S7" s="4" t="inlineStr">
         <is>
           <t>У работодателя по месту проведения СОУТ</t>
         </is>
       </c>
-      <c r="R7" s="4" t="inlineStr">
+      <c r="T7" s="4" t="inlineStr">
         <is>
           <t>45 лет по месту проведения СОУТ; при вредных/опасных условиях труда — 50 лет (документы, законченные делопроизводством после 01.01.2003) / 75 лет (до 01.01.2003); в других организациях — 5 лет (п. 407 Перечня, утв. приказом Росархива от 20.12.2019 № 236)</t>
         </is>
       </c>
-      <c r="S7" s="4" t="inlineStr">
+      <c r="U7" s="4" t="inlineStr">
         <is>
           <t>Бумажная и электронная</t>
         </is>
@@ -1279,55 +1349,65 @@
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
           <t>собственноручная или НЭП или УКЭП</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>не предусмотрено</t>
-        </is>
-      </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>включается в отчет о проведении СОУТ; указание вредных и (или) опасных производственных факторов, идентифицированных на рабочих местах</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
           <t>ЧАСТИЧНО</t>
         </is>
       </c>
-      <c r="L8" s="4" t="inlineStr">
+      <c r="N8" s="4" t="inlineStr">
         <is>
           <t>Сведения о рабочих местах, на которых проведена СОУТ, и распределение по классам (подклассам) условий труда — ст. 18</t>
         </is>
       </c>
-      <c r="M8" s="4" t="inlineStr">
+      <c r="O8" s="4" t="inlineStr">
         <is>
           <t>Федеральная государственная информационная система учета результатов проведения специальной оценки условий труда (ФГИС учета результатов СОУТ)</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="P8" s="4" t="inlineStr">
         <is>
           <t>Организация, проводящая СОУТ; Комиссия по СОУТ</t>
         </is>
       </c>
-      <c r="O8" s="4" t="inlineStr">
+      <c r="Q8" s="4" t="inlineStr">
         <is>
           <t>Организация, проводящая СОУТ — формирует и передаёт сведения в ФГИС; Комиссия по СОУТ — утверждает в составе отчета</t>
         </is>
       </c>
-      <c r="P8" s="4" t="inlineStr">
+      <c r="R8" s="4" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="Q8" s="4" t="inlineStr">
+      <c r="S8" s="4" t="inlineStr">
         <is>
           <t>У работодателя по месту проведения СОУТ</t>
         </is>
       </c>
-      <c r="R8" s="4" t="inlineStr">
+      <c r="T8" s="4" t="inlineStr">
         <is>
           <t>45 лет по месту проведения СОУТ; при вредных/опасных условиях труда — 50 лет (документы, законченные делопроизводством после 01.01.2003) / 75 лет (до 01.01.2003); в других организациях — 5 лет (п. 407 Перечня, утв. приказом Росархива от 20.12.2019 № 236)</t>
         </is>
       </c>
-      <c r="S8" s="4" t="inlineStr">
+      <c r="U8" s="4" t="inlineStr">
         <is>
           <t>Бумажная и электронная</t>
         </is>
@@ -1374,55 +1454,65 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
           <t>собственноручная или НЭП или УКЭП</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>оформляются в отношении каждого идентифицированного вредного и (или) опасного производственного фактора</t>
-        </is>
-      </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>оформляются в отношении каждого идентифицированного вредного и (или) опасного производственного фактора; включаются в отчет</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
           <t>ЧАСТИЧНО</t>
         </is>
       </c>
-      <c r="L9" s="4" t="inlineStr">
+      <c r="N9" s="4" t="inlineStr">
         <is>
           <t>Измеренные значения вредных и (или) опасных производственных факторов, единицы измерения, нормативы, продолжительность воздействия — ст. 18 ч. 2</t>
         </is>
       </c>
-      <c r="M9" s="4" t="inlineStr">
+      <c r="O9" s="4" t="inlineStr">
         <is>
           <t>Федеральная государственная информационная система учета результатов проведения специальной оценки условий труда (ФГИС учета результатов СОУТ)</t>
         </is>
       </c>
-      <c r="N9" s="4" t="inlineStr">
+      <c r="P9" s="4" t="inlineStr">
         <is>
           <t>Организация, проводящая СОУТ; Комиссия по СОУТ</t>
         </is>
       </c>
-      <c r="O9" s="4" t="inlineStr">
+      <c r="Q9" s="4" t="inlineStr">
         <is>
           <t>Организация, проводящая СОУТ — оформляет протоколы и передаёт сведения измерений в ФГИС; Комиссия по СОУТ — принимает результаты в рамках отчета</t>
         </is>
       </c>
-      <c r="P9" s="4" t="inlineStr">
+      <c r="R9" s="4" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="Q9" s="4" t="inlineStr">
+      <c r="S9" s="4" t="inlineStr">
         <is>
           <t>У работодателя по месту проведения СОУТ</t>
         </is>
       </c>
-      <c r="R9" s="4" t="inlineStr">
+      <c r="T9" s="4" t="inlineStr">
         <is>
           <t>45 лет по месту проведения СОУТ; при вредных/опасных условиях труда — 50 лет (документы, законченные делопроизводством после 01.01.2003) / 75 лет (до 01.01.2003); в других организациях — 5 лет (п. 407 Перечня, утв. приказом Росархива от 20.12.2019 № 236)</t>
         </is>
       </c>
-      <c r="S9" s="4" t="inlineStr">
+      <c r="U9" s="4" t="inlineStr">
         <is>
           <t>Бумажная и электронная</t>
         </is>
@@ -1469,55 +1559,65 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
           <t>собственноручная или НЭП или УКЭП</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>не предусмотрено</t>
-        </is>
-      </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>оформляется при проведении такой оценки; включается в отчет</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
           <t>ЧАСТИЧНО</t>
         </is>
       </c>
-      <c r="L10" s="4" t="inlineStr">
+      <c r="N10" s="4" t="inlineStr">
         <is>
           <t>Сведения о снижении класса (подкласса) условий труда на основании оценки эффективности СИЗ, включая реквизиты протокола — ст. 18 ч. 2</t>
         </is>
       </c>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="O10" s="4" t="inlineStr">
         <is>
           <t>Федеральная государственная информационная система учета результатов проведения специальной оценки условий труда (ФГИС учета результатов СОУТ)</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="P10" s="4" t="inlineStr">
         <is>
           <t>Организация, проводящая СОУТ; Комиссия по СОУТ</t>
         </is>
       </c>
-      <c r="O10" s="4" t="inlineStr">
+      <c r="Q10" s="4" t="inlineStr">
         <is>
           <t>Организация, проводящая СОУТ — оформляет протокол и передаёт сведения в ФГИС; Комиссия по СОУТ — утверждает в составе отчета</t>
         </is>
       </c>
-      <c r="P10" s="4" t="inlineStr">
+      <c r="R10" s="4" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="Q10" s="4" t="inlineStr">
+      <c r="S10" s="4" t="inlineStr">
         <is>
           <t>У работодателя по месту проведения СОУТ</t>
         </is>
       </c>
-      <c r="R10" s="4" t="inlineStr">
+      <c r="T10" s="4" t="inlineStr">
         <is>
           <t>45 лет по месту проведения СОУТ; при вредных/опасных условиях труда — 50 лет (документы, законченные делопроизводством после 01.01.2003) / 75 лет (до 01.01.2003); в других организациях — 5 лет (п. 407 Перечня, утв. приказом Росархива от 20.12.2019 № 236)</t>
         </is>
       </c>
-      <c r="S10" s="4" t="inlineStr">
+      <c r="U10" s="4" t="inlineStr">
         <is>
           <t>Бумажная и электронная</t>
         </is>
@@ -1564,51 +1664,61 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
           <t>собственноручная</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>не предусмотрено</t>
-        </is>
-      </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>должен содержать обоснование решения; является неотъемлемой частью отчета; копия направляется в территориальный орган ГИТ</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
           <t>НЕТ</t>
         </is>
       </c>
-      <c r="L11" s="4" t="inlineStr">
+      <c r="N11" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M11" s="4" t="n"/>
-      <c r="N11" s="4" t="inlineStr">
+      <c r="O11" s="4" t="n"/>
+      <c r="P11" s="4" t="inlineStr">
         <is>
           <t>Работодатель; Территориальный орган ГИТ</t>
         </is>
       </c>
-      <c r="O11" s="4" t="inlineStr">
+      <c r="Q11" s="4" t="inlineStr">
         <is>
           <t>Работодатель — направляет копию протокола в территориальный орган ГИТ; ГИТ — получает копию</t>
         </is>
       </c>
-      <c r="P11" s="4" t="inlineStr">
+      <c r="R11" s="4" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="Q11" s="4" t="inlineStr">
+      <c r="S11" s="4" t="inlineStr">
         <is>
           <t>У работодателя по месту проведения СОУТ</t>
         </is>
       </c>
-      <c r="R11" s="4" t="inlineStr">
+      <c r="T11" s="4" t="inlineStr">
         <is>
           <t>45 лет по месту проведения СОУТ; при вредных/опасных условиях труда — 50 лет (документы, законченные делопроизводством после 01.01.2003) / 75 лет (до 01.01.2003); в других организациях — 5 лет (п. 407 Перечня, утв. приказом Росархива от 20.12.2019 № 236)</t>
         </is>
       </c>
-      <c r="S11" s="4" t="inlineStr">
+      <c r="U11" s="4" t="inlineStr">
         <is>
           <t>Бумажная и электронная</t>
         </is>
@@ -1655,55 +1765,65 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
           <t>собственноручная или НЭП или УКЭП</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>не предусмотрено</t>
-        </is>
-      </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>включается в отчет о проведении СОУТ</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
           <t>ЧАСТИЧНО</t>
         </is>
       </c>
-      <c r="L12" s="4" t="inlineStr">
+      <c r="N12" s="4" t="inlineStr">
         <is>
           <t>Сводные сведения о количестве рабочих мест и распределении рабочих мест по классам (подклассам) условий труда — ст. 18 ч. 2</t>
         </is>
       </c>
-      <c r="M12" s="4" t="inlineStr">
+      <c r="O12" s="4" t="inlineStr">
         <is>
           <t>Федеральная государственная информационная система учета результатов проведения специальной оценки условий труда (ФГИС учета результатов СОУТ)</t>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="P12" s="4" t="inlineStr">
         <is>
           <t>Организация, проводящая СОУТ; Работодатель; Комиссия по СОУТ</t>
         </is>
       </c>
-      <c r="O12" s="4" t="inlineStr">
+      <c r="Q12" s="4" t="inlineStr">
         <is>
           <t>Организация, проводящая СОУТ — формирует и передаёт сведения в ФГИС; Комиссия по СОУТ — утверждает в составе отчета; Работодатель — размещает сводные данные на сайте (при наличии)</t>
         </is>
       </c>
-      <c r="P12" s="4" t="inlineStr">
+      <c r="R12" s="4" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="Q12" s="4" t="inlineStr">
+      <c r="S12" s="4" t="inlineStr">
         <is>
           <t>У работодателя по месту проведения СОУТ</t>
         </is>
       </c>
-      <c r="R12" s="4" t="inlineStr">
+      <c r="T12" s="4" t="inlineStr">
         <is>
           <t>45 лет по месту проведения СОУТ; при вредных/опасных условиях труда — 50 лет (документы, законченные делопроизводством после 01.01.2003) / 75 лет (до 01.01.2003); в других организациях — 5 лет (п. 407 Перечня, утв. приказом Росархива от 20.12.2019 № 236)</t>
         </is>
       </c>
-      <c r="S12" s="4" t="inlineStr">
+      <c r="U12" s="4" t="inlineStr">
         <is>
           <t>Бумажная и электронная</t>
         </is>
@@ -1750,43 +1870,53 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
           <t>собственноручная или НЭП или УКЭП</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>для аналогичных рабочих мест разрабатывается единый перечень</t>
-        </is>
-      </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>включается в отчет; для аналогичных рабочих мест — единый перечень; сводные данные подлежат размещению на сайте работодателя (при наличии сайта)</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
           <t>НЕТ</t>
         </is>
       </c>
-      <c r="L13" s="4" t="inlineStr">
+      <c r="N13" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M13" s="4" t="n"/>
-      <c r="N13" s="4" t="n"/>
       <c r="O13" s="4" t="n"/>
-      <c r="P13" s="4" t="inlineStr">
+      <c r="P13" s="4" t="n"/>
+      <c r="Q13" s="4" t="n"/>
+      <c r="R13" s="4" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="Q13" s="4" t="inlineStr">
+      <c r="S13" s="4" t="inlineStr">
         <is>
           <t>У работодателя по месту проведения СОУТ</t>
         </is>
       </c>
-      <c r="R13" s="4" t="inlineStr">
+      <c r="T13" s="4" t="inlineStr">
         <is>
           <t>45 лет по месту проведения СОУТ; при вредных/опасных условиях труда — 50 лет (документы, законченные делопроизводством после 01.01.2003) / 75 лет (до 01.01.2003); в других организациях — 5 лет (п. 407 Перечня, утв. приказом Росархива от 20.12.2019 № 236)</t>
         </is>
       </c>
-      <c r="S13" s="4" t="inlineStr">
+      <c r="U13" s="4" t="inlineStr">
         <is>
           <t>Бумажная и электронная</t>
         </is>
@@ -1833,55 +1963,65 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
           <t>собственноручная или НЭП или УКЭП</t>
         </is>
       </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>не предусмотрено</t>
-        </is>
-      </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>включается в отчет о проведении СОУТ</t>
+        </is>
+      </c>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
           <t>ЧАСТИЧНО</t>
         </is>
       </c>
-      <c r="L14" s="4" t="inlineStr">
+      <c r="N14" s="4" t="inlineStr">
         <is>
           <t>Сведения о результатах проведения СОУТ (классы/подклассы, факторы и связанные данные учета) — ст. 18</t>
         </is>
       </c>
-      <c r="M14" s="4" t="inlineStr">
+      <c r="O14" s="4" t="inlineStr">
         <is>
           <t>Федеральная государственная информационная система учета результатов проведения специальной оценки условий труда (ФГИС учета результатов СОУТ)</t>
         </is>
       </c>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="P14" s="4" t="inlineStr">
         <is>
           <t>Эксперт организации, проводящей СОУТ; Организация, проводящая СОУТ; Комиссия по СОУТ</t>
         </is>
       </c>
-      <c r="O14" s="4" t="inlineStr">
+      <c r="Q14" s="4" t="inlineStr">
         <is>
           <t>Эксперт — готовит заключение; Организация, проводящая СОУТ — передаёт результаты в ФГИС; Комиссия по СОУТ — утверждает отчет</t>
         </is>
       </c>
-      <c r="P14" s="4" t="inlineStr">
+      <c r="R14" s="4" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="Q14" s="4" t="inlineStr">
+      <c r="S14" s="4" t="inlineStr">
         <is>
           <t>У работодателя по месту проведения СОУТ</t>
         </is>
       </c>
-      <c r="R14" s="4" t="inlineStr">
+      <c r="T14" s="4" t="inlineStr">
         <is>
           <t>45 лет по месту проведения СОУТ; при вредных/опасных условиях труда — 50 лет (документы, законченные делопроизводством после 01.01.2003) / 75 лет (до 01.01.2003); в других организациях — 5 лет (п. 407 Перечня, утв. приказом Росархива от 20.12.2019 № 236)</t>
         </is>
       </c>
-      <c r="S14" s="4" t="inlineStr">
+      <c r="U14" s="4" t="inlineStr">
         <is>
           <t>Бумажная и электронная</t>
         </is>
@@ -1928,43 +2068,53 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
           <t>собственноручная</t>
         </is>
       </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>не предусмотрено</t>
-        </is>
-      </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>письменная форма; при наличии прилагаются к отчету; работодатель обязан рассмотреть</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
           <t>НЕТ</t>
         </is>
       </c>
-      <c r="L15" s="4" t="inlineStr">
+      <c r="N15" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M15" s="4" t="n"/>
-      <c r="N15" s="4" t="n"/>
       <c r="O15" s="4" t="n"/>
-      <c r="P15" s="4" t="inlineStr">
+      <c r="P15" s="4" t="n"/>
+      <c r="Q15" s="4" t="n"/>
+      <c r="R15" s="4" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="Q15" s="4" t="inlineStr">
+      <c r="S15" s="4" t="inlineStr">
         <is>
           <t>У работодателя по месту проведения СОУТ</t>
         </is>
       </c>
-      <c r="R15" s="4" t="inlineStr">
+      <c r="T15" s="4" t="inlineStr">
         <is>
           <t>45 лет по месту проведения СОУТ; при вредных/опасных условиях труда — 50 лет (документы, законченные делопроизводством после 01.01.2003) / 75 лет (до 01.01.2003); в других организациях — 5 лет (п. 407 Перечня, утв. приказом Росархива от 20.12.2019 № 236)</t>
         </is>
       </c>
-      <c r="S15" s="4" t="inlineStr">
+      <c r="U15" s="4" t="inlineStr">
         <is>
           <t>Бумажная</t>
         </is>
@@ -2011,43 +2161,53 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
           <t>собственноручная</t>
         </is>
       </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>не предусмотрено</t>
-        </is>
-      </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>письменная форма; прилагается к отчету о проведении СОУТ</t>
+        </is>
+      </c>
+      <c r="M16" s="4" t="inlineStr">
+        <is>
           <t>НЕТ</t>
         </is>
       </c>
-      <c r="L16" s="4" t="inlineStr">
+      <c r="N16" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M16" s="4" t="n"/>
-      <c r="N16" s="4" t="n"/>
       <c r="O16" s="4" t="n"/>
-      <c r="P16" s="4" t="inlineStr">
+      <c r="P16" s="4" t="n"/>
+      <c r="Q16" s="4" t="n"/>
+      <c r="R16" s="4" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="Q16" s="4" t="inlineStr">
+      <c r="S16" s="4" t="inlineStr">
         <is>
           <t>У работодателя по месту проведения СОУТ</t>
         </is>
       </c>
-      <c r="R16" s="4" t="inlineStr">
+      <c r="T16" s="4" t="inlineStr">
         <is>
           <t>45 лет по месту проведения СОУТ; при вредных/опасных условиях труда — 50 лет (документы, законченные делопроизводством после 01.01.2003) / 75 лет (до 01.01.2003); в других организациях — 5 лет (п. 407 Перечня, утв. приказом Росархива от 20.12.2019 № 236)</t>
         </is>
       </c>
-      <c r="S16" s="4" t="inlineStr">
+      <c r="U16" s="4" t="inlineStr">
         <is>
           <t>Бумажная</t>
         </is>
@@ -2094,55 +2254,65 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
           <t>собственноручная или УКЭП</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>подается в территориальный орган федерального надзора в сфере труда по месту нахождения работодателя</t>
-        </is>
-      </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>подача по утверждённой форме и порядку в территориальный орган ГИТ по месту нахождения работодателя; внесение в реестр деклараций</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="L17" s="4" t="inlineStr">
+      <c r="N17" s="4" t="inlineStr">
         <is>
           <t>Полностью документ</t>
         </is>
       </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="O17" s="4" t="inlineStr">
         <is>
           <t>Реестр деклараций соответствия условий труда государственным нормативным требованиям охраны труда; сведения о результатах СОУТ также учитываются в: Федеральная государственная информационная система учета результатов проведения специальной оценки условий труда (ФГИС учета результатов СОУТ)</t>
         </is>
       </c>
-      <c r="N17" s="4" t="inlineStr">
+      <c r="P17" s="4" t="inlineStr">
         <is>
           <t>Работодатель; Территориальный орган ГИТ (уполномоченный орган); Организация, проводящая СОУТ</t>
         </is>
       </c>
-      <c r="O17" s="4" t="inlineStr">
+      <c r="Q17" s="4" t="inlineStr">
         <is>
           <t>Работодатель — подаёт декларацию; Уполномоченный орган / ГИТ — формирует и ведёт реестр деклараций; Организация, проводящая СОУТ — передаёт связанные результаты СОУТ в ФГИС</t>
         </is>
       </c>
-      <c r="P17" s="4" t="inlineStr">
+      <c r="R17" s="4" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="Q17" s="4" t="inlineStr">
+      <c r="S17" s="4" t="inlineStr">
         <is>
           <t>У работодателя по месту проведения СОУТ; реестр ведётся уполномоченным органом</t>
         </is>
       </c>
-      <c r="R17" s="4" t="inlineStr">
+      <c r="T17" s="4" t="inlineStr">
         <is>
           <t>45 лет по месту проведения СОУТ; при вредных/опасных условиях труда — 50 лет (документы, законченные делопроизводством после 01.01.2003) / 75 лет (до 01.01.2003); в других организациях — 5 лет (п. 407 Перечня, утв. приказом Росархива от 20.12.2019 № 236); декларация бессрочна при сохранении условий труда (ст. 11 ч. 4)</t>
         </is>
       </c>
-      <c r="S17" s="4" t="inlineStr">
+      <c r="U17" s="4" t="inlineStr">
         <is>
           <t>Бумажная и электронная</t>
         </is>
@@ -2189,43 +2359,53 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
           <t>собственноручная или УКЭП</t>
         </is>
       </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>уведомление — любым доступным способом с подтверждением факта; копия отчета — заказным почтовым отправлением с уведомлением о вручении либо электронный документ, подписанный УКЭП; срок — 3 рабочих дня со дня утверждения отчета</t>
-        </is>
-      </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>в течение 3 рабочих дней со дня утверждения отчета; способ уведомления — с подтверждением факта; копия отчета — заказным почтовым отправлением с уведомлением о вручении либо электронный документ, подписанный УКЭП</t>
+        </is>
+      </c>
+      <c r="M18" s="4" t="inlineStr">
+        <is>
           <t>НЕТ</t>
         </is>
       </c>
-      <c r="L18" s="4" t="inlineStr">
+      <c r="N18" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M18" s="4" t="n"/>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="O18" s="4" t="n"/>
+      <c r="P18" s="4" t="inlineStr">
         <is>
           <t>Работодатель; Организация, проводившая СОУТ</t>
         </is>
       </c>
-      <c r="O18" s="4" t="inlineStr">
+      <c r="Q18" s="4" t="inlineStr">
         <is>
           <t>Работодатель — уведомляет и направляет копию; Организация, проводившая СОУТ — получает копию и далее передаёт сведения в ФГИС</t>
         </is>
       </c>
-      <c r="P18" s="4" t="inlineStr">
+      <c r="R18" s="4" t="inlineStr">
         <is>
           <t>НЕТ</t>
         </is>
       </c>
-      <c r="Q18" s="4" t="n"/>
-      <c r="R18" s="4" t="n"/>
       <c r="S18" s="4" t="n"/>
+      <c r="T18" s="4" t="n"/>
+      <c r="U18" s="4" t="n"/>
     </row>
     <row r="19" ht="75" customHeight="1">
       <c r="A19" s="4" t="n">
@@ -2268,43 +2448,53 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
           <t>собственноручная</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>ознакомление под роспись не позднее 30 календарных дней со дня утверждения отчета</t>
-        </is>
-      </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>ознакомление под роспись не позднее 30 календарных дней со дня утверждения отчета (без периодов нетрудоспособности, отпуска, командировки, междувахтового отдыха)</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
           <t>НЕТ</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="N19" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M19" s="4" t="n"/>
-      <c r="N19" s="4" t="n"/>
       <c r="O19" s="4" t="n"/>
-      <c r="P19" s="4" t="inlineStr">
+      <c r="P19" s="4" t="n"/>
+      <c r="Q19" s="4" t="n"/>
+      <c r="R19" s="4" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="Q19" s="4" t="inlineStr">
+      <c r="S19" s="4" t="inlineStr">
         <is>
           <t>У работодателя по месту проведения СОУТ</t>
         </is>
       </c>
-      <c r="R19" s="4" t="inlineStr">
+      <c r="T19" s="4" t="inlineStr">
         <is>
           <t>45 лет по месту проведения СОУТ; при вредных/опасных условиях труда — 50 лет (документы, законченные делопроизводством после 01.01.2003) / 75 лет (до 01.01.2003); в других организациях — 5 лет (п. 407 Перечня, утв. приказом Росархива от 20.12.2019 № 236)</t>
         </is>
       </c>
-      <c r="S19" s="4" t="inlineStr">
+      <c r="U19" s="4" t="inlineStr">
         <is>
           <t>Бумажная</t>
         </is>
@@ -2351,35 +2541,45 @@
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
           <t>не предусмотрено</t>
         </is>
       </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>размещение на официальном сайте (при наличии) не позднее 30 календарных дней со дня утверждения отчета; с учётом требований о персональных данных и охраняемой тайне</t>
-        </is>
-      </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>размещение на официальном сайте работодателя (при наличии) не позднее 30 календарных дней со дня утверждения отчета; с учётом требований законодательства о персональных данных и охраняемой тайне; печать/прошивка/регистрация не предусмотрены</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
           <t>НЕТ</t>
         </is>
       </c>
-      <c r="L20" s="4" t="inlineStr">
+      <c r="N20" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M20" s="4" t="n"/>
-      <c r="N20" s="4" t="n"/>
       <c r="O20" s="4" t="n"/>
-      <c r="P20" s="4" t="inlineStr">
+      <c r="P20" s="4" t="n"/>
+      <c r="Q20" s="4" t="n"/>
+      <c r="R20" s="4" t="inlineStr">
         <is>
           <t>НЕТ</t>
         </is>
       </c>
-      <c r="Q20" s="4" t="n"/>
-      <c r="R20" s="4" t="n"/>
       <c r="S20" s="4" t="n"/>
+      <c r="T20" s="4" t="n"/>
+      <c r="U20" s="4" t="n"/>
     </row>
     <row r="21" ht="75" customHeight="1">
       <c r="A21" s="4" t="n">
@@ -2422,43 +2622,53 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
           <t>собственноручная</t>
         </is>
       </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>не предусмотрено</t>
-        </is>
-      </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>направление копии протокола в территориальный орган ГИТ по месту нахождения работодателя; печать/прошивка не предусмотрены</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
           <t>НЕТ</t>
         </is>
       </c>
-      <c r="L21" s="4" t="inlineStr">
+      <c r="N21" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M21" s="4" t="n"/>
-      <c r="N21" s="4" t="inlineStr">
+      <c r="O21" s="4" t="n"/>
+      <c r="P21" s="4" t="inlineStr">
         <is>
           <t>Работодатель; Территориальный орган ГИТ</t>
         </is>
       </c>
-      <c r="O21" s="4" t="inlineStr">
+      <c r="Q21" s="4" t="inlineStr">
         <is>
           <t>Работодатель — направляет копию; ГИТ — получает</t>
         </is>
       </c>
-      <c r="P21" s="4" t="inlineStr">
+      <c r="R21" s="4" t="inlineStr">
         <is>
           <t>НЕТ</t>
         </is>
       </c>
-      <c r="Q21" s="4" t="n"/>
-      <c r="R21" s="4" t="n"/>
       <c r="S21" s="4" t="n"/>
+      <c r="T21" s="4" t="n"/>
+      <c r="U21" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/presentations/Analiz_NPA_FZ_426_dokumenty_SOUT.xlsx
+++ b/presentations/Analiz_NPA_FZ_426_dokumenty_SOUT.xlsx
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:V21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="28" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" style="2" min="1" max="1"/>
@@ -598,8 +598,8 @@
     <col width="22" customWidth="1" style="2" min="9" max="15"/>
     <col width="24" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="40" customWidth="1" min="12" max="12"/>
-    <col width="28" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="12" max="12"/>
+    <col width="45" customWidth="1" min="13" max="13"/>
     <col width="36" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="24" customWidth="1" style="2" min="16" max="16384"/>
@@ -668,47 +668,52 @@
           <t>Требования к ведению документооборота (печать, нумерация, прошивка и т.п)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
+        <is>
+          <t>Иные требования и комментарии (порядок оформления, сроки, направление и т.п.)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Передача в ГИС</t>
         </is>
       </c>
-      <c r="N1" s="5" t="inlineStr">
+      <c r="O1" s="5" t="inlineStr">
         <is>
           <t>Что передается</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Название ГИС или реестра </t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Участник передачи документа СУОТ в ГИС (работник, работодатель, руководитель, специалист по ОТ, включая третьих лиц:  СФР, ГИТ, профсоюзы, аккредитованные организации и пр.)</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Роль участника передачи документа СУОТ в ГИС (инициация, согласование, подписание, передача и т.д)</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>требования к хранению (да/нет)</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>место хранения</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>сроки  хранения</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>форма хранения</t>
         </is>
@@ -775,33 +780,38 @@
       </c>
       <c r="M2" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N2" s="4" t="inlineStr">
+        <is>
           <t>НЕТ</t>
         </is>
       </c>
-      <c r="N2" s="4" t="inlineStr">
+      <c r="O2" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O2" s="4" t="n"/>
       <c r="P2" s="4" t="n"/>
       <c r="Q2" s="4" t="n"/>
-      <c r="R2" s="4" t="inlineStr">
+      <c r="R2" s="4" t="n"/>
+      <c r="S2" s="4" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="S2" s="4" t="inlineStr">
+      <c r="T2" s="4" t="inlineStr">
         <is>
           <t>У работодателя по месту проведения СОУТ</t>
         </is>
       </c>
-      <c r="T2" s="4" t="inlineStr">
+      <c r="U2" s="4" t="inlineStr">
         <is>
           <t>45 лет (как документ к материалам СОУТ / решение по организации СОУТ; п. 407 Перечня Росархива № 236 — по аналогии с решениями к СОУТ)</t>
         </is>
       </c>
-      <c r="U2" s="4" t="inlineStr">
+      <c r="V2" s="4" t="inlineStr">
         <is>
           <t>Бумажная</t>
         </is>
@@ -868,33 +878,38 @@
       </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
           <t>НЕТ</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O3" s="4" t="n"/>
       <c r="P3" s="4" t="n"/>
       <c r="Q3" s="4" t="n"/>
-      <c r="R3" s="4" t="inlineStr">
+      <c r="R3" s="4" t="n"/>
+      <c r="S3" s="4" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="S3" s="4" t="inlineStr">
+      <c r="T3" s="4" t="inlineStr">
         <is>
           <t>У работодателя по месту проведения СОУТ</t>
         </is>
       </c>
-      <c r="T3" s="4" t="inlineStr">
+      <c r="U3" s="4" t="inlineStr">
         <is>
           <t>45 лет по месту проведения СОУТ; при вредных/опасных условиях труда — 50 лет (документы, законченные делопроизводством после 01.01.2003) / 75 лет (до 01.01.2003); в других организациях — 5 лет (п. 407 Перечня, утв. приказом Росархива от 20.12.2019 № 236)</t>
         </is>
       </c>
-      <c r="U3" s="4" t="inlineStr">
+      <c r="V3" s="4" t="inlineStr">
         <is>
           <t>Бумажная</t>
         </is>
@@ -951,55 +966,60 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>утверждение комиссией до начала работ по СОУТ; указание аналогичных рабочих мест</t>
+          <t>не предусмотрено</t>
         </is>
       </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
+          <t>Утверждается комиссией до начала работ по СОУТ; указываются аналогичные рабочие места</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
           <t>ЧАСТИЧНО</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>Сведения о рабочих местах (индивидуальный номер РМ, профессия/должность, численность работников, класс/подкласс условий труда и связанные показатели) в составе результатов СОУТ — ст. 18 ч. 2</t>
         </is>
       </c>
-      <c r="O4" s="4" t="inlineStr">
+      <c r="P4" s="4" t="inlineStr">
         <is>
           <t>Федеральная государственная информационная система учета результатов проведения специальной оценки условий труда (ФГИС учета результатов СОУТ)</t>
         </is>
       </c>
-      <c r="P4" s="4" t="inlineStr">
+      <c r="Q4" s="4" t="inlineStr">
         <is>
           <t>Организация, проводящая СОУТ; Работодатель; Комиссия по СОУТ</t>
         </is>
       </c>
-      <c r="Q4" s="4" t="inlineStr">
+      <c r="R4" s="4" t="inlineStr">
         <is>
           <t>Комиссия по СОУТ — утверждает перечень; Организация, проводящая СОУТ — передаёт сведения о рабочих местах в составе результатов СОУТ; Работодатель — обеспечивает проведение СОУТ</t>
         </is>
       </c>
-      <c r="R4" s="4" t="inlineStr">
+      <c r="S4" s="4" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="S4" s="4" t="inlineStr">
+      <c r="T4" s="4" t="inlineStr">
         <is>
           <t>У работодателя по месту проведения СОУТ</t>
         </is>
       </c>
-      <c r="T4" s="4" t="inlineStr">
+      <c r="U4" s="4" t="inlineStr">
         <is>
           <t>45 лет по месту проведения СОУТ; при вредных/опасных условиях труда — 50 лет (документы, законченные делопроизводством после 01.01.2003) / 75 лет (до 01.01.2003); в других организациях — 5 лет (п. 407 Перечня, утв. приказом Росархива от 20.12.2019 № 236)</t>
         </is>
       </c>
-      <c r="U4" s="4" t="inlineStr">
+      <c r="V4" s="4" t="inlineStr">
         <is>
           <t>Бумажная и электронная</t>
         </is>
@@ -1056,47 +1076,52 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>заключение до начала работ; организация СОУТ не позднее 5 рабочих дней со дня заключения договора передаёт сведения в ФГИС и сообщает работодателю идентификационный номер</t>
+          <t>не предусмотрено</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
+          <t>Заключается до начала работ; организация, проводящая СОУТ, не позднее 5 рабочих дней со дня заключения договора передаёт сведения в ФГИС и сообщает работодателю идентификационный номер</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
           <t>ЧАСТИЧНО</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
+      <c r="O5" s="4" t="inlineStr">
         <is>
           <t>Сведения о работодателе и об организации, проводящей СОУТ (для присвоения идентификационного номера предстоящей СОУТ) — ст. 8 ч. 6, ст. 18 (подп. «а», «в», «в.1» п. 1 ч. 2 и др.)</t>
         </is>
       </c>
-      <c r="O5" s="4" t="inlineStr">
+      <c r="P5" s="4" t="inlineStr">
         <is>
           <t>Федеральная государственная информационная система учета результатов проведения специальной оценки условий труда (ФГИС учета результатов СОУТ)</t>
         </is>
       </c>
-      <c r="P5" s="4" t="inlineStr">
+      <c r="Q5" s="4" t="inlineStr">
         <is>
           <t>Организация, проводящая СОУТ; Работодатель</t>
         </is>
       </c>
-      <c r="Q5" s="4" t="inlineStr">
+      <c r="R5" s="4" t="inlineStr">
         <is>
           <t>Организация, проводящая СОУТ — передаёт в ФГИС сведения после заключения договора и получает идентификационный номер; Работодатель — заключает договор, получает идентификационный номер</t>
         </is>
       </c>
-      <c r="R5" s="4" t="inlineStr">
+      <c r="S5" s="4" t="inlineStr">
         <is>
           <t>НЕТ</t>
         </is>
       </c>
-      <c r="S5" s="4" t="n"/>
       <c r="T5" s="4" t="n"/>
       <c r="U5" s="4" t="n"/>
+      <c r="V5" s="4" t="n"/>
     </row>
     <row r="6" ht="75" customHeight="1">
       <c r="A6" s="4" t="n">
@@ -1149,55 +1174,60 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>бумажный носитель или электронный документ; подписание всеми членами комиссии; утверждение председателем комиссии не позднее 30 календарных дней со дня направления работодателю; наличие идентификационного номера; особое мнение члена комиссии прилагается письменно (при наличии)</t>
+          <t>не предусмотрено</t>
         </is>
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
+          <t>Допускается бумажный носитель или электронный документ; подписывается всеми членами комиссии; утверждается председателем комиссии не позднее 30 календарных дней со дня направления работодателю; должен содержать идентификационный номер; особое мнение члена комиссии прилагается письменно (при наличии)</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <t>Полностью документ</t>
         </is>
       </c>
-      <c r="O6" s="4" t="inlineStr">
+      <c r="P6" s="4" t="inlineStr">
         <is>
           <t>Федеральная государственная информационная система учета результатов проведения специальной оценки условий труда (ФГИС учета результатов СОУТ)</t>
         </is>
       </c>
-      <c r="P6" s="4" t="inlineStr">
+      <c r="Q6" s="4" t="inlineStr">
         <is>
           <t>Организация, проводящая СОУТ; Работодатель; Комиссия по СОУТ; Председатель комиссии по СОУТ</t>
         </is>
       </c>
-      <c r="Q6" s="4" t="inlineStr">
+      <c r="R6" s="4" t="inlineStr">
         <is>
           <t>Члены комиссии — подписывают отчет; Председатель комиссии — утверждает отчет; Работодатель — уведомляет организацию СОУТ и направляет копию утвержденного отчета; Организация, проводящая СОУТ — передаёт сведения о результатах в ФГИС</t>
         </is>
       </c>
-      <c r="R6" s="4" t="inlineStr">
+      <c r="S6" s="4" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="S6" s="4" t="inlineStr">
+      <c r="T6" s="4" t="inlineStr">
         <is>
           <t>У работодателя по месту проведения СОУТ; экземпляр/сведения также у организации, проводившей СОУТ</t>
         </is>
       </c>
-      <c r="T6" s="4" t="inlineStr">
+      <c r="U6" s="4" t="inlineStr">
         <is>
           <t>45 лет по месту проведения СОУТ; при вредных/опасных условиях труда — 50 лет (документы, законченные делопроизводством после 01.01.2003) / 75 лет (до 01.01.2003); в других организациях — 5 лет (п. 407 Перечня, утв. приказом Росархива от 20.12.2019 № 236)</t>
         </is>
       </c>
-      <c r="U6" s="4" t="inlineStr">
+      <c r="V6" s="4" t="inlineStr">
         <is>
           <t>Бумажная и электронная</t>
         </is>
@@ -1254,55 +1284,60 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>оформляется в составе отчета; на аналогичные рабочие места заполняется одна карта</t>
+          <t>не предусмотрено</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
+          <t>Оформляется в составе отчета; на аналогичные рабочие места заполняется одна карта</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
           <t>ЧАСТИЧНО</t>
         </is>
       </c>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="O7" s="4" t="inlineStr">
         <is>
           <t>Сведения по рабочему месту: класс (подкласс) условий труда, вредные/опасные факторы, измеренные значения, продолжительность воздействия, сведения о снижении класса на основании оценки эффективности СИЗ — ст. 18 ч. 2</t>
         </is>
       </c>
-      <c r="O7" s="4" t="inlineStr">
+      <c r="P7" s="4" t="inlineStr">
         <is>
           <t>Федеральная государственная информационная система учета результатов проведения специальной оценки условий труда (ФГИС учета результатов СОУТ)</t>
         </is>
       </c>
-      <c r="P7" s="4" t="inlineStr">
+      <c r="Q7" s="4" t="inlineStr">
         <is>
           <t>Организация, проводящая СОУТ; Комиссия по СОУТ; Работник</t>
         </is>
       </c>
-      <c r="Q7" s="4" t="inlineStr">
+      <c r="R7" s="4" t="inlineStr">
         <is>
           <t>Организация, проводящая СОУТ — формирует карты и передаёт сведения в ФГИС; Комиссия по СОУТ — утверждает в составе отчета; Работник — ознакамливается с результатами</t>
         </is>
       </c>
-      <c r="R7" s="4" t="inlineStr">
+      <c r="S7" s="4" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="S7" s="4" t="inlineStr">
+      <c r="T7" s="4" t="inlineStr">
         <is>
           <t>У работодателя по месту проведения СОУТ</t>
         </is>
       </c>
-      <c r="T7" s="4" t="inlineStr">
+      <c r="U7" s="4" t="inlineStr">
         <is>
           <t>45 лет по месту проведения СОУТ; при вредных/опасных условиях труда — 50 лет (документы, законченные делопроизводством после 01.01.2003) / 75 лет (до 01.01.2003); в других организациях — 5 лет (п. 407 Перечня, утв. приказом Росархива от 20.12.2019 № 236)</t>
         </is>
       </c>
-      <c r="U7" s="4" t="inlineStr">
+      <c r="V7" s="4" t="inlineStr">
         <is>
           <t>Бумажная и электронная</t>
         </is>
@@ -1359,55 +1394,60 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>включается в отчет о проведении СОУТ; указание вредных и (или) опасных производственных факторов, идентифицированных на рабочих местах</t>
+          <t>не предусмотрено</t>
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
+          <t>Включается в отчет о проведении СОУТ; указываются вредные и (или) опасные производственные факторы, идентифицированные на рабочих местах</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
           <t>ЧАСТИЧНО</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="O8" s="4" t="inlineStr">
         <is>
           <t>Сведения о рабочих местах, на которых проведена СОУТ, и распределение по классам (подклассам) условий труда — ст. 18</t>
         </is>
       </c>
-      <c r="O8" s="4" t="inlineStr">
+      <c r="P8" s="4" t="inlineStr">
         <is>
           <t>Федеральная государственная информационная система учета результатов проведения специальной оценки условий труда (ФГИС учета результатов СОУТ)</t>
         </is>
       </c>
-      <c r="P8" s="4" t="inlineStr">
+      <c r="Q8" s="4" t="inlineStr">
         <is>
           <t>Организация, проводящая СОУТ; Комиссия по СОУТ</t>
         </is>
       </c>
-      <c r="Q8" s="4" t="inlineStr">
+      <c r="R8" s="4" t="inlineStr">
         <is>
           <t>Организация, проводящая СОУТ — формирует и передаёт сведения в ФГИС; Комиссия по СОУТ — утверждает в составе отчета</t>
         </is>
       </c>
-      <c r="R8" s="4" t="inlineStr">
+      <c r="S8" s="4" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="S8" s="4" t="inlineStr">
+      <c r="T8" s="4" t="inlineStr">
         <is>
           <t>У работодателя по месту проведения СОУТ</t>
         </is>
       </c>
-      <c r="T8" s="4" t="inlineStr">
+      <c r="U8" s="4" t="inlineStr">
         <is>
           <t>45 лет по месту проведения СОУТ; при вредных/опасных условиях труда — 50 лет (документы, законченные делопроизводством после 01.01.2003) / 75 лет (до 01.01.2003); в других организациях — 5 лет (п. 407 Перечня, утв. приказом Росархива от 20.12.2019 № 236)</t>
         </is>
       </c>
-      <c r="U8" s="4" t="inlineStr">
+      <c r="V8" s="4" t="inlineStr">
         <is>
           <t>Бумажная и электронная</t>
         </is>
@@ -1464,55 +1504,60 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>оформляются в отношении каждого идентифицированного вредного и (или) опасного производственного фактора; включаются в отчет</t>
+          <t>не предусмотрено</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
+          <t>Оформляются в отношении каждого идентифицированного вредного и (или) опасного производственного фактора; включаются в отчет</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
           <t>ЧАСТИЧНО</t>
         </is>
       </c>
-      <c r="N9" s="4" t="inlineStr">
+      <c r="O9" s="4" t="inlineStr">
         <is>
           <t>Измеренные значения вредных и (или) опасных производственных факторов, единицы измерения, нормативы, продолжительность воздействия — ст. 18 ч. 2</t>
         </is>
       </c>
-      <c r="O9" s="4" t="inlineStr">
+      <c r="P9" s="4" t="inlineStr">
         <is>
           <t>Федеральная государственная информационная система учета результатов проведения специальной оценки условий труда (ФГИС учета результатов СОУТ)</t>
         </is>
       </c>
-      <c r="P9" s="4" t="inlineStr">
+      <c r="Q9" s="4" t="inlineStr">
         <is>
           <t>Организация, проводящая СОУТ; Комиссия по СОУТ</t>
         </is>
       </c>
-      <c r="Q9" s="4" t="inlineStr">
+      <c r="R9" s="4" t="inlineStr">
         <is>
           <t>Организация, проводящая СОУТ — оформляет протоколы и передаёт сведения измерений в ФГИС; Комиссия по СОУТ — принимает результаты в рамках отчета</t>
         </is>
       </c>
-      <c r="R9" s="4" t="inlineStr">
+      <c r="S9" s="4" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="S9" s="4" t="inlineStr">
+      <c r="T9" s="4" t="inlineStr">
         <is>
           <t>У работодателя по месту проведения СОУТ</t>
         </is>
       </c>
-      <c r="T9" s="4" t="inlineStr">
+      <c r="U9" s="4" t="inlineStr">
         <is>
           <t>45 лет по месту проведения СОУТ; при вредных/опасных условиях труда — 50 лет (документы, законченные делопроизводством после 01.01.2003) / 75 лет (до 01.01.2003); в других организациях — 5 лет (п. 407 Перечня, утв. приказом Росархива от 20.12.2019 № 236)</t>
         </is>
       </c>
-      <c r="U9" s="4" t="inlineStr">
+      <c r="V9" s="4" t="inlineStr">
         <is>
           <t>Бумажная и электронная</t>
         </is>
@@ -1569,55 +1614,60 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>оформляется при проведении такой оценки; включается в отчет</t>
+          <t>не предусмотрено</t>
         </is>
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
+          <t>Оформляется при проведении такой оценки; включается в отчет</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
           <t>ЧАСТИЧНО</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="O10" s="4" t="inlineStr">
         <is>
           <t>Сведения о снижении класса (подкласса) условий труда на основании оценки эффективности СИЗ, включая реквизиты протокола — ст. 18 ч. 2</t>
         </is>
       </c>
-      <c r="O10" s="4" t="inlineStr">
+      <c r="P10" s="4" t="inlineStr">
         <is>
           <t>Федеральная государственная информационная система учета результатов проведения специальной оценки условий труда (ФГИС учета результатов СОУТ)</t>
         </is>
       </c>
-      <c r="P10" s="4" t="inlineStr">
+      <c r="Q10" s="4" t="inlineStr">
         <is>
           <t>Организация, проводящая СОУТ; Комиссия по СОУТ</t>
         </is>
       </c>
-      <c r="Q10" s="4" t="inlineStr">
+      <c r="R10" s="4" t="inlineStr">
         <is>
           <t>Организация, проводящая СОУТ — оформляет протокол и передаёт сведения в ФГИС; Комиссия по СОУТ — утверждает в составе отчета</t>
         </is>
       </c>
-      <c r="R10" s="4" t="inlineStr">
+      <c r="S10" s="4" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="S10" s="4" t="inlineStr">
+      <c r="T10" s="4" t="inlineStr">
         <is>
           <t>У работодателя по месту проведения СОУТ</t>
         </is>
       </c>
-      <c r="T10" s="4" t="inlineStr">
+      <c r="U10" s="4" t="inlineStr">
         <is>
           <t>45 лет по месту проведения СОУТ; при вредных/опасных условиях труда — 50 лет (документы, законченные делопроизводством после 01.01.2003) / 75 лет (до 01.01.2003); в других организациях — 5 лет (п. 407 Перечня, утв. приказом Росархива от 20.12.2019 № 236)</t>
         </is>
       </c>
-      <c r="U10" s="4" t="inlineStr">
+      <c r="V10" s="4" t="inlineStr">
         <is>
           <t>Бумажная и электронная</t>
         </is>
@@ -1674,51 +1724,56 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>должен содержать обоснование решения; является неотъемлемой частью отчета; копия направляется в территориальный орган ГИТ</t>
+          <t>не предусмотрено</t>
         </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
+          <t>Должен содержать обоснование решения; является неотъемлемой частью отчета; копия направляется в территориальный орган ГИТ</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
           <t>НЕТ</t>
         </is>
       </c>
-      <c r="N11" s="4" t="inlineStr">
+      <c r="O11" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O11" s="4" t="n"/>
-      <c r="P11" s="4" t="inlineStr">
+      <c r="P11" s="4" t="n"/>
+      <c r="Q11" s="4" t="inlineStr">
         <is>
           <t>Работодатель; Территориальный орган ГИТ</t>
         </is>
       </c>
-      <c r="Q11" s="4" t="inlineStr">
+      <c r="R11" s="4" t="inlineStr">
         <is>
           <t>Работодатель — направляет копию протокола в территориальный орган ГИТ; ГИТ — получает копию</t>
         </is>
       </c>
-      <c r="R11" s="4" t="inlineStr">
+      <c r="S11" s="4" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="S11" s="4" t="inlineStr">
+      <c r="T11" s="4" t="inlineStr">
         <is>
           <t>У работодателя по месту проведения СОУТ</t>
         </is>
       </c>
-      <c r="T11" s="4" t="inlineStr">
+      <c r="U11" s="4" t="inlineStr">
         <is>
           <t>45 лет по месту проведения СОУТ; при вредных/опасных условиях труда — 50 лет (документы, законченные делопроизводством после 01.01.2003) / 75 лет (до 01.01.2003); в других организациях — 5 лет (п. 407 Перечня, утв. приказом Росархива от 20.12.2019 № 236)</t>
         </is>
       </c>
-      <c r="U11" s="4" t="inlineStr">
+      <c r="V11" s="4" t="inlineStr">
         <is>
           <t>Бумажная и электронная</t>
         </is>
@@ -1775,55 +1830,60 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>включается в отчет о проведении СОУТ</t>
+          <t>не предусмотрено</t>
         </is>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
+          <t>Включается в отчет о проведении СОУТ</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
           <t>ЧАСТИЧНО</t>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="O12" s="4" t="inlineStr">
         <is>
           <t>Сводные сведения о количестве рабочих мест и распределении рабочих мест по классам (подклассам) условий труда — ст. 18 ч. 2</t>
         </is>
       </c>
-      <c r="O12" s="4" t="inlineStr">
+      <c r="P12" s="4" t="inlineStr">
         <is>
           <t>Федеральная государственная информационная система учета результатов проведения специальной оценки условий труда (ФГИС учета результатов СОУТ)</t>
         </is>
       </c>
-      <c r="P12" s="4" t="inlineStr">
+      <c r="Q12" s="4" t="inlineStr">
         <is>
           <t>Организация, проводящая СОУТ; Работодатель; Комиссия по СОУТ</t>
         </is>
       </c>
-      <c r="Q12" s="4" t="inlineStr">
+      <c r="R12" s="4" t="inlineStr">
         <is>
           <t>Организация, проводящая СОУТ — формирует и передаёт сведения в ФГИС; Комиссия по СОУТ — утверждает в составе отчета; Работодатель — размещает сводные данные на сайте (при наличии)</t>
         </is>
       </c>
-      <c r="R12" s="4" t="inlineStr">
+      <c r="S12" s="4" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="S12" s="4" t="inlineStr">
+      <c r="T12" s="4" t="inlineStr">
         <is>
           <t>У работодателя по месту проведения СОУТ</t>
         </is>
       </c>
-      <c r="T12" s="4" t="inlineStr">
+      <c r="U12" s="4" t="inlineStr">
         <is>
           <t>45 лет по месту проведения СОУТ; при вредных/опасных условиях труда — 50 лет (документы, законченные делопроизводством после 01.01.2003) / 75 лет (до 01.01.2003); в других организациях — 5 лет (п. 407 Перечня, утв. приказом Росархива от 20.12.2019 № 236)</t>
         </is>
       </c>
-      <c r="U12" s="4" t="inlineStr">
+      <c r="V12" s="4" t="inlineStr">
         <is>
           <t>Бумажная и электронная</t>
         </is>
@@ -1880,43 +1940,48 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>включается в отчет; для аналогичных рабочих мест — единый перечень; сводные данные подлежат размещению на сайте работодателя (при наличии сайта)</t>
+          <t>не предусмотрено</t>
         </is>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
+          <t>Включается в отчет; для аналогичных рабочих мест разрабатывается единый перечень; сводные данные подлежат размещению на сайте работодателя (при наличии сайта)</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
           <t>НЕТ</t>
         </is>
       </c>
-      <c r="N13" s="4" t="inlineStr">
+      <c r="O13" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O13" s="4" t="n"/>
       <c r="P13" s="4" t="n"/>
       <c r="Q13" s="4" t="n"/>
-      <c r="R13" s="4" t="inlineStr">
+      <c r="R13" s="4" t="n"/>
+      <c r="S13" s="4" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="S13" s="4" t="inlineStr">
+      <c r="T13" s="4" t="inlineStr">
         <is>
           <t>У работодателя по месту проведения СОУТ</t>
         </is>
       </c>
-      <c r="T13" s="4" t="inlineStr">
+      <c r="U13" s="4" t="inlineStr">
         <is>
           <t>45 лет по месту проведения СОУТ; при вредных/опасных условиях труда — 50 лет (документы, законченные делопроизводством после 01.01.2003) / 75 лет (до 01.01.2003); в других организациях — 5 лет (п. 407 Перечня, утв. приказом Росархива от 20.12.2019 № 236)</t>
         </is>
       </c>
-      <c r="U13" s="4" t="inlineStr">
+      <c r="V13" s="4" t="inlineStr">
         <is>
           <t>Бумажная и электронная</t>
         </is>
@@ -1973,55 +2038,60 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>включается в отчет о проведении СОУТ</t>
+          <t>не предусмотрено</t>
         </is>
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
+          <t>Включается в отчет о проведении СОУТ</t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
           <t>ЧАСТИЧНО</t>
         </is>
       </c>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="O14" s="4" t="inlineStr">
         <is>
           <t>Сведения о результатах проведения СОУТ (классы/подклассы, факторы и связанные данные учета) — ст. 18</t>
         </is>
       </c>
-      <c r="O14" s="4" t="inlineStr">
+      <c r="P14" s="4" t="inlineStr">
         <is>
           <t>Федеральная государственная информационная система учета результатов проведения специальной оценки условий труда (ФГИС учета результатов СОУТ)</t>
         </is>
       </c>
-      <c r="P14" s="4" t="inlineStr">
+      <c r="Q14" s="4" t="inlineStr">
         <is>
           <t>Эксперт организации, проводящей СОУТ; Организация, проводящая СОУТ; Комиссия по СОУТ</t>
         </is>
       </c>
-      <c r="Q14" s="4" t="inlineStr">
+      <c r="R14" s="4" t="inlineStr">
         <is>
           <t>Эксперт — готовит заключение; Организация, проводящая СОУТ — передаёт результаты в ФГИС; Комиссия по СОУТ — утверждает отчет</t>
         </is>
       </c>
-      <c r="R14" s="4" t="inlineStr">
+      <c r="S14" s="4" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="S14" s="4" t="inlineStr">
+      <c r="T14" s="4" t="inlineStr">
         <is>
           <t>У работодателя по месту проведения СОУТ</t>
         </is>
       </c>
-      <c r="T14" s="4" t="inlineStr">
+      <c r="U14" s="4" t="inlineStr">
         <is>
           <t>45 лет по месту проведения СОУТ; при вредных/опасных условиях труда — 50 лет (документы, законченные делопроизводством после 01.01.2003) / 75 лет (до 01.01.2003); в других организациях — 5 лет (п. 407 Перечня, утв. приказом Росархива от 20.12.2019 № 236)</t>
         </is>
       </c>
-      <c r="U14" s="4" t="inlineStr">
+      <c r="V14" s="4" t="inlineStr">
         <is>
           <t>Бумажная и электронная</t>
         </is>
@@ -2078,43 +2148,48 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>письменная форма; при наличии прилагаются к отчету; работодатель обязан рассмотреть</t>
+          <t>не предусмотрено</t>
         </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
+          <t>Письменная форма; при наличии прилагаются к отчету; работодатель обязан рассмотреть</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
           <t>НЕТ</t>
         </is>
       </c>
-      <c r="N15" s="4" t="inlineStr">
+      <c r="O15" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O15" s="4" t="n"/>
       <c r="P15" s="4" t="n"/>
       <c r="Q15" s="4" t="n"/>
-      <c r="R15" s="4" t="inlineStr">
+      <c r="R15" s="4" t="n"/>
+      <c r="S15" s="4" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="S15" s="4" t="inlineStr">
+      <c r="T15" s="4" t="inlineStr">
         <is>
           <t>У работодателя по месту проведения СОУТ</t>
         </is>
       </c>
-      <c r="T15" s="4" t="inlineStr">
+      <c r="U15" s="4" t="inlineStr">
         <is>
           <t>45 лет по месту проведения СОУТ; при вредных/опасных условиях труда — 50 лет (документы, законченные делопроизводством после 01.01.2003) / 75 лет (до 01.01.2003); в других организациях — 5 лет (п. 407 Перечня, утв. приказом Росархива от 20.12.2019 № 236)</t>
         </is>
       </c>
-      <c r="U15" s="4" t="inlineStr">
+      <c r="V15" s="4" t="inlineStr">
         <is>
           <t>Бумажная</t>
         </is>
@@ -2171,43 +2246,48 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>письменная форма; прилагается к отчету о проведении СОУТ</t>
+          <t>не предусмотрено</t>
         </is>
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
+          <t>Письменная форма; прилагается к отчету о проведении СОУТ</t>
+        </is>
+      </c>
+      <c r="N16" s="4" t="inlineStr">
+        <is>
           <t>НЕТ</t>
         </is>
       </c>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="O16" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O16" s="4" t="n"/>
       <c r="P16" s="4" t="n"/>
       <c r="Q16" s="4" t="n"/>
-      <c r="R16" s="4" t="inlineStr">
+      <c r="R16" s="4" t="n"/>
+      <c r="S16" s="4" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="S16" s="4" t="inlineStr">
+      <c r="T16" s="4" t="inlineStr">
         <is>
           <t>У работодателя по месту проведения СОУТ</t>
         </is>
       </c>
-      <c r="T16" s="4" t="inlineStr">
+      <c r="U16" s="4" t="inlineStr">
         <is>
           <t>45 лет по месту проведения СОУТ; при вредных/опасных условиях труда — 50 лет (документы, законченные делопроизводством после 01.01.2003) / 75 лет (до 01.01.2003); в других организациях — 5 лет (п. 407 Перечня, утв. приказом Росархива от 20.12.2019 № 236)</t>
         </is>
       </c>
-      <c r="U16" s="4" t="inlineStr">
+      <c r="V16" s="4" t="inlineStr">
         <is>
           <t>Бумажная</t>
         </is>
@@ -2264,55 +2344,60 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>подача по утверждённой форме и порядку в территориальный орган ГИТ по месту нахождения работодателя; внесение в реестр деклараций</t>
+          <t>не предусмотрено</t>
         </is>
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
+          <t>Подаётся по утверждённой форме и порядку в территориальный орган ГИТ по месту нахождения работодателя; вносится в реестр деклараций</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="N17" s="4" t="inlineStr">
+      <c r="O17" s="4" t="inlineStr">
         <is>
           <t>Полностью документ</t>
         </is>
       </c>
-      <c r="O17" s="4" t="inlineStr">
+      <c r="P17" s="4" t="inlineStr">
         <is>
           <t>Реестр деклараций соответствия условий труда государственным нормативным требованиям охраны труда; сведения о результатах СОУТ также учитываются в: Федеральная государственная информационная система учета результатов проведения специальной оценки условий труда (ФГИС учета результатов СОУТ)</t>
         </is>
       </c>
-      <c r="P17" s="4" t="inlineStr">
+      <c r="Q17" s="4" t="inlineStr">
         <is>
           <t>Работодатель; Территориальный орган ГИТ (уполномоченный орган); Организация, проводящая СОУТ</t>
         </is>
       </c>
-      <c r="Q17" s="4" t="inlineStr">
+      <c r="R17" s="4" t="inlineStr">
         <is>
           <t>Работодатель — подаёт декларацию; Уполномоченный орган / ГИТ — формирует и ведёт реестр деклараций; Организация, проводящая СОУТ — передаёт связанные результаты СОУТ в ФГИС</t>
         </is>
       </c>
-      <c r="R17" s="4" t="inlineStr">
+      <c r="S17" s="4" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="S17" s="4" t="inlineStr">
+      <c r="T17" s="4" t="inlineStr">
         <is>
           <t>У работодателя по месту проведения СОУТ; реестр ведётся уполномоченным органом</t>
         </is>
       </c>
-      <c r="T17" s="4" t="inlineStr">
+      <c r="U17" s="4" t="inlineStr">
         <is>
           <t>45 лет по месту проведения СОУТ; при вредных/опасных условиях труда — 50 лет (документы, законченные делопроизводством после 01.01.2003) / 75 лет (до 01.01.2003); в других организациях — 5 лет (п. 407 Перечня, утв. приказом Росархива от 20.12.2019 № 236); декларация бессрочна при сохранении условий труда (ст. 11 ч. 4)</t>
         </is>
       </c>
-      <c r="U17" s="4" t="inlineStr">
+      <c r="V17" s="4" t="inlineStr">
         <is>
           <t>Бумажная и электронная</t>
         </is>
@@ -2369,43 +2454,48 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>в течение 3 рабочих дней со дня утверждения отчета; способ уведомления — с подтверждением факта; копия отчета — заказным почтовым отправлением с уведомлением о вручении либо электронный документ, подписанный УКЭП</t>
+          <t>не предусмотрено</t>
         </is>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
+          <t>В течение 3 рабочих дней со дня утверждения отчета; способ уведомления — с подтверждением факта; копия отчета — заказным почтовым отправлением с уведомлением о вручении либо электронный документ, подписанный УКЭП</t>
+        </is>
+      </c>
+      <c r="N18" s="4" t="inlineStr">
+        <is>
           <t>НЕТ</t>
         </is>
       </c>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="O18" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O18" s="4" t="n"/>
-      <c r="P18" s="4" t="inlineStr">
+      <c r="P18" s="4" t="n"/>
+      <c r="Q18" s="4" t="inlineStr">
         <is>
           <t>Работодатель; Организация, проводившая СОУТ</t>
         </is>
       </c>
-      <c r="Q18" s="4" t="inlineStr">
+      <c r="R18" s="4" t="inlineStr">
         <is>
           <t>Работодатель — уведомляет и направляет копию; Организация, проводившая СОУТ — получает копию и далее передаёт сведения в ФГИС</t>
         </is>
       </c>
-      <c r="R18" s="4" t="inlineStr">
+      <c r="S18" s="4" t="inlineStr">
         <is>
           <t>НЕТ</t>
         </is>
       </c>
-      <c r="S18" s="4" t="n"/>
       <c r="T18" s="4" t="n"/>
       <c r="U18" s="4" t="n"/>
+      <c r="V18" s="4" t="n"/>
     </row>
     <row r="19" ht="75" customHeight="1">
       <c r="A19" s="4" t="n">
@@ -2458,43 +2548,48 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>ознакомление под роспись не позднее 30 календарных дней со дня утверждения отчета (без периодов нетрудоспособности, отпуска, командировки, междувахтового отдыха)</t>
+          <t>не предусмотрено</t>
         </is>
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
+          <t>Ознакомление под роспись не позднее 30 календарных дней со дня утверждения отчета (без периодов нетрудоспособности, отпуска, командировки, междувахтового отдыха)</t>
+        </is>
+      </c>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
           <t>НЕТ</t>
         </is>
       </c>
-      <c r="N19" s="4" t="inlineStr">
+      <c r="O19" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O19" s="4" t="n"/>
       <c r="P19" s="4" t="n"/>
       <c r="Q19" s="4" t="n"/>
-      <c r="R19" s="4" t="inlineStr">
+      <c r="R19" s="4" t="n"/>
+      <c r="S19" s="4" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="S19" s="4" t="inlineStr">
+      <c r="T19" s="4" t="inlineStr">
         <is>
           <t>У работодателя по месту проведения СОУТ</t>
         </is>
       </c>
-      <c r="T19" s="4" t="inlineStr">
+      <c r="U19" s="4" t="inlineStr">
         <is>
           <t>45 лет по месту проведения СОУТ; при вредных/опасных условиях труда — 50 лет (документы, законченные делопроизводством после 01.01.2003) / 75 лет (до 01.01.2003); в других организациях — 5 лет (п. 407 Перечня, утв. приказом Росархива от 20.12.2019 № 236)</t>
         </is>
       </c>
-      <c r="U19" s="4" t="inlineStr">
+      <c r="V19" s="4" t="inlineStr">
         <is>
           <t>Бумажная</t>
         </is>
@@ -2551,35 +2646,40 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>размещение на официальном сайте работодателя (при наличии) не позднее 30 календарных дней со дня утверждения отчета; с учётом требований законодательства о персональных данных и охраняемой тайне; печать/прошивка/регистрация не предусмотрены</t>
+          <t>не предусмотрено</t>
         </is>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
+          <t>Размещение на официальном сайте работодателя (при наличии) не позднее 30 календарных дней со дня утверждения отчета; с учётом требований законодательства о персональных данных и охраняемой тайне</t>
+        </is>
+      </c>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
           <t>НЕТ</t>
         </is>
       </c>
-      <c r="N20" s="4" t="inlineStr">
+      <c r="O20" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O20" s="4" t="n"/>
       <c r="P20" s="4" t="n"/>
       <c r="Q20" s="4" t="n"/>
-      <c r="R20" s="4" t="inlineStr">
+      <c r="R20" s="4" t="n"/>
+      <c r="S20" s="4" t="inlineStr">
         <is>
           <t>НЕТ</t>
         </is>
       </c>
-      <c r="S20" s="4" t="n"/>
       <c r="T20" s="4" t="n"/>
       <c r="U20" s="4" t="n"/>
+      <c r="V20" s="4" t="n"/>
     </row>
     <row r="21" ht="75" customHeight="1">
       <c r="A21" s="4" t="n">
@@ -2632,43 +2732,48 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>направление копии протокола в территориальный орган ГИТ по месту нахождения работодателя; печать/прошивка не предусмотрены</t>
+          <t>не предусмотрено</t>
         </is>
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
+          <t>Направляется в территориальный орган ГИТ по месту нахождения работодателя</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
           <t>НЕТ</t>
         </is>
       </c>
-      <c r="N21" s="4" t="inlineStr">
+      <c r="O21" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O21" s="4" t="n"/>
-      <c r="P21" s="4" t="inlineStr">
+      <c r="P21" s="4" t="n"/>
+      <c r="Q21" s="4" t="inlineStr">
         <is>
           <t>Работодатель; Территориальный орган ГИТ</t>
         </is>
       </c>
-      <c r="Q21" s="4" t="inlineStr">
+      <c r="R21" s="4" t="inlineStr">
         <is>
           <t>Работодатель — направляет копию; ГИТ — получает</t>
         </is>
       </c>
-      <c r="R21" s="4" t="inlineStr">
+      <c r="S21" s="4" t="inlineStr">
         <is>
           <t>НЕТ</t>
         </is>
       </c>
-      <c r="S21" s="4" t="n"/>
       <c r="T21" s="4" t="n"/>
       <c r="U21" s="4" t="n"/>
+      <c r="V21" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
